--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_SKALA USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_SKALA USAHA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,212 +417,212 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Jumlah Prelist UB</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Jumlah UB yang Berhasil Didata</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Persentase UB yang Berhasil Didata</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Jumlah Prelist UMKM (UM + UMK)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Jumlah UMKM yang Berhasil Didata (UM + UMK)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Persentase UMKM yang Berhasil Didata (UM + UMK)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Total Usaha Didata (UB + UM + UMK)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>
@@ -693,13 +681,13 @@
         <v>50</v>
       </c>
       <c r="N2" t="n">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="O2" t="n">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="P2" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
@@ -708,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -717,31 +705,31 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="Y2" t="n">
-        <v>343</v>
+        <v>393</v>
       </c>
       <c r="Z2" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="AA2" t="n">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="AB2" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="AD2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -753,16 +741,16 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="AK2" t="n">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="AL2" t="n">
         <v>364</v>
@@ -973,10 +961,10 @@
         <v>40</v>
       </c>
       <c r="N4" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="O4" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -985,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -997,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -1006,13 +994,13 @@
         <v>429</v>
       </c>
       <c r="Y4" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="Z4" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="AA4" t="n">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -1021,7 +1009,7 @@
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -1033,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
@@ -1042,7 +1030,7 @@
         <v>429</v>
       </c>
       <c r="AK4" t="n">
-        <v>252</v>
+        <v>269</v>
       </c>
       <c r="AL4" t="n">
         <v>363</v>
@@ -1116,7 +1104,7 @@
         <v>219</v>
       </c>
       <c r="O5" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1137,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
         <v>425</v>
@@ -1152,7 +1140,7 @@
         <v>219</v>
       </c>
       <c r="AA5" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1173,10 +1161,10 @@
         <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="n">
         <v>425</v>
@@ -1253,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O6" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1277,28 +1265,28 @@
         <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="Y6" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="Z6" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AA6" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1313,16 +1301,16 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AK6" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="AL6" t="n">
         <v>354</v>
@@ -1393,13 +1381,13 @@
         <v>20</v>
       </c>
       <c r="N7" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="O7" t="n">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1423,19 +1411,19 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Y7" t="n">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="Z7" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="AA7" t="n">
-        <v>253</v>
+        <v>275</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1459,10 +1447,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AK7" t="n">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="AL7" t="n">
         <v>336</v>
@@ -1533,16 +1521,16 @@
         <v>30</v>
       </c>
       <c r="N8" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="O8" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="Q8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1563,22 +1551,22 @@
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="Y8" t="n">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="Z8" t="n">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="AA8" t="n">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="AB8" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1599,10 +1587,10 @@
         <v>1</v>
       </c>
       <c r="AJ8" t="n">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="AK8" t="n">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="AL8" t="n">
         <v>304</v>
@@ -1673,13 +1661,13 @@
         <v>20</v>
       </c>
       <c r="N9" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="O9" t="n">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="P9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1703,19 +1691,19 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Y9" t="n">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="Z9" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="AA9" t="n">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="AB9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
@@ -1739,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AK9" t="n">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="AL9" t="n">
         <v>288</v>
@@ -1816,16 +1804,16 @@
         <v>186</v>
       </c>
       <c r="O10" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1852,16 +1840,16 @@
         <v>186</v>
       </c>
       <c r="AA10" t="n">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="AB10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
         <v>7</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1953,19 +1941,19 @@
         <v>30</v>
       </c>
       <c r="N11" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="O11" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="P11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1977,31 +1965,31 @@
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>407</v>
       </c>
       <c r="Y11" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="Z11" t="n">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="AA11" t="n">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="AB11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -2013,16 +2001,16 @@
         <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
         <v>407</v>
       </c>
       <c r="AK11" t="n">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="AL11" t="n">
         <v>373</v>
@@ -2093,13 +2081,13 @@
         <v>170</v>
       </c>
       <c r="N12" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="O12" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="P12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
@@ -2117,25 +2105,25 @@
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="Y12" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="Z12" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="AA12" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="AB12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>1</v>
@@ -2153,16 +2141,16 @@
         <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="AK12" t="n">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AL12" t="n">
         <v>383</v>
@@ -2233,13 +2221,13 @@
         <v>100</v>
       </c>
       <c r="N13" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="O13" t="n">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2263,19 +2251,19 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="Y13" t="n">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="Z13" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="AA13" t="n">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="AB13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2299,10 +2287,10 @@
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AK13" t="n">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="AL13" t="n">
         <v>373</v>
@@ -2373,16 +2361,16 @@
         <v>50</v>
       </c>
       <c r="N14" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="O14" t="n">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="P14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2406,19 +2394,19 @@
         <v>426</v>
       </c>
       <c r="Y14" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="Z14" t="n">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="AA14" t="n">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="AB14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2442,7 +2430,7 @@
         <v>426</v>
       </c>
       <c r="AK14" t="n">
-        <v>237</v>
+        <v>251</v>
       </c>
       <c r="AL14" t="n">
         <v>364</v>
@@ -2513,13 +2501,13 @@
         <v>60</v>
       </c>
       <c r="N15" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="O15" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="P15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
         <v>1</v>
@@ -2537,25 +2525,25 @@
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Y15" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="Z15" t="n">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="AA15" t="n">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="AB15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="AC15" t="n">
         <v>1</v>
@@ -2573,16 +2561,16 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AK15" t="n">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AL15" t="n">
         <v>324</v>
@@ -2653,13 +2641,13 @@
         <v>510</v>
       </c>
       <c r="N16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="O16" t="n">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="P16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -2668,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -2680,22 +2668,22 @@
         <v>30</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="Y16" t="n">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="Z16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AA16" t="n">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="AB16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2704,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2716,13 +2704,13 @@
         <v>30</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="AK16" t="n">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="AL16" t="n">
         <v>288</v>
@@ -2793,25 +2781,25 @@
         <v>160</v>
       </c>
       <c r="N17" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="O17" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2823,31 +2811,31 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="Y17" t="n">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="Z17" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="AA17" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE17" t="n">
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -2859,10 +2847,10 @@
         <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AK17" t="n">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="AL17" t="n">
         <v>370</v>
@@ -2933,19 +2921,19 @@
         <v>70</v>
       </c>
       <c r="N18" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="O18" t="n">
-        <v>199</v>
+        <v>225</v>
       </c>
       <c r="P18" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="Q18" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -2963,25 +2951,25 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="Y18" t="n">
-        <v>311</v>
+        <v>350</v>
       </c>
       <c r="Z18" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="AA18" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="AB18" t="n">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="AC18" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
@@ -2999,10 +2987,10 @@
         <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AK18" t="n">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AL18" t="n">
         <v>366</v>
@@ -3073,13 +3061,13 @@
         <v>100</v>
       </c>
       <c r="N19" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="O19" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="P19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -3106,16 +3094,16 @@
         <v>454</v>
       </c>
       <c r="Y19" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Z19" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AA19" t="n">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="AB19" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3142,7 +3130,7 @@
         <v>454</v>
       </c>
       <c r="AK19" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL19" t="n">
         <v>423</v>
@@ -3356,10 +3344,10 @@
         <v>186</v>
       </c>
       <c r="O21" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>2</v>
@@ -3377,7 +3365,7 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -3392,10 +3380,10 @@
         <v>186</v>
       </c>
       <c r="AA21" t="n">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="AB21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>2</v>
@@ -3413,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
         <v>0</v>
@@ -3493,16 +3481,16 @@
         <v>90</v>
       </c>
       <c r="N22" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="O22" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="R22" t="n">
         <v>7</v>
@@ -3523,22 +3511,22 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="Y22" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Z22" t="n">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AA22" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="AD22" t="n">
         <v>7</v>
@@ -3559,10 +3547,10 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AK22" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL22" t="n">
         <v>410</v>
@@ -3633,19 +3621,19 @@
         <v>70</v>
       </c>
       <c r="N23" t="n">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="O23" t="n">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -3663,25 +3651,25 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Y23" t="n">
+        <v>313</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>220</v>
+      </c>
+      <c r="AA23" t="n">
         <v>296</v>
       </c>
-      <c r="Z23" t="n">
-        <v>236</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>286</v>
-      </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
@@ -3699,10 +3687,10 @@
         <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AK23" t="n">
-        <v>296</v>
+        <v>313</v>
       </c>
       <c r="AL23" t="n">
         <v>450</v>
@@ -3773,22 +3761,22 @@
         <v>40</v>
       </c>
       <c r="N24" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="O24" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="P24" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="Q24" t="n">
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="S24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
@@ -3797,7 +3785,7 @@
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
@@ -3806,25 +3794,25 @@
         <v>402</v>
       </c>
       <c r="Y24" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="Z24" t="n">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="AA24" t="n">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="AB24" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="AC24" t="n">
         <v>1</v>
       </c>
       <c r="AD24" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3833,7 +3821,7 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="AI24" t="n">
         <v>0</v>
@@ -3842,7 +3830,7 @@
         <v>402</v>
       </c>
       <c r="AK24" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AL24" t="n">
         <v>359</v>
@@ -3913,13 +3901,13 @@
         <v>60</v>
       </c>
       <c r="N25" t="n">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="O25" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -3943,19 +3931,19 @@
         <v>1</v>
       </c>
       <c r="X25" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="Y25" t="n">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="Z25" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="AA25" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3979,10 +3967,10 @@
         <v>1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="AK25" t="n">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="AL25" t="n">
         <v>308</v>
@@ -4053,25 +4041,25 @@
         <v>80</v>
       </c>
       <c r="N26" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="O26" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="P26" t="n">
+        <v>18</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>20</v>
+      </c>
+      <c r="R26" t="n">
         <v>7</v>
       </c>
-      <c r="Q26" t="n">
-        <v>19</v>
-      </c>
-      <c r="R26" t="n">
-        <v>11</v>
-      </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -4086,28 +4074,28 @@
         <v>472</v>
       </c>
       <c r="Y26" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="Z26" t="n">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="AA26" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AB26" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD26" t="n">
         <v>7</v>
       </c>
-      <c r="AC26" t="n">
-        <v>19</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>11</v>
-      </c>
       <c r="AE26" t="n">
         <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -4122,7 +4110,7 @@
         <v>472</v>
       </c>
       <c r="AK26" t="n">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AL26" t="n">
         <v>419</v>
@@ -4193,13 +4181,13 @@
         <v>260</v>
       </c>
       <c r="N27" t="n">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="O27" t="n">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -4223,19 +4211,19 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="Y27" t="n">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="Z27" t="n">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="AA27" t="n">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="AB27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -4259,10 +4247,10 @@
         <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AK27" t="n">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="AL27" t="n">
         <v>342</v>
@@ -4333,19 +4321,19 @@
         <v>60</v>
       </c>
       <c r="N28" t="n">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="O28" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -4357,31 +4345,31 @@
         <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="Y28" t="n">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="Z28" t="n">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="AA28" t="n">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="AB28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AC28" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4393,16 +4381,16 @@
         <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AK28" t="n">
-        <v>237</v>
+        <v>263</v>
       </c>
       <c r="AL28" t="n">
         <v>384</v>
@@ -4473,13 +4461,13 @@
         <v>60</v>
       </c>
       <c r="N29" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="O29" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -4497,25 +4485,25 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="Y29" t="n">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="Z29" t="n">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="AA29" t="n">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="AB29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -4533,16 +4521,16 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AI29" t="n">
         <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="AK29" t="n">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="AL29" t="n">
         <v>357</v>
@@ -4613,22 +4601,22 @@
         <v>170</v>
       </c>
       <c r="N30" t="n">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="O30" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="P30" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
         <v>0</v>
@@ -4637,34 +4625,34 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>516</v>
+        <v>526</v>
       </c>
       <c r="Y30" t="n">
-        <v>332</v>
+        <v>356</v>
       </c>
       <c r="Z30" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AA30" t="n">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4679,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="AK30" t="n">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="AL30" t="n">
         <v>457</v>
@@ -4756,13 +4744,13 @@
         <v>8</v>
       </c>
       <c r="O31" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="P31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Q31" t="n">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -4786,19 +4774,19 @@
         <v>332</v>
       </c>
       <c r="Y31" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="Z31" t="n">
         <v>8</v>
       </c>
       <c r="AA31" t="n">
-        <v>69</v>
+        <v>100</v>
       </c>
       <c r="AB31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AC31" t="n">
-        <v>203</v>
+        <v>178</v>
       </c>
       <c r="AD31" t="n">
         <v>0</v>
@@ -4822,7 +4810,7 @@
         <v>332</v>
       </c>
       <c r="AK31" t="n">
-        <v>121</v>
+        <v>146</v>
       </c>
       <c r="AL31" t="n">
         <v>315</v>
@@ -4893,19 +4881,19 @@
         <v>50</v>
       </c>
       <c r="N32" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O32" t="n">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="P32" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -4917,31 +4905,31 @@
         <v>1</v>
       </c>
       <c r="V32" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="W32" t="n">
         <v>3</v>
       </c>
       <c r="X32" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Y32" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Z32" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AA32" t="n">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="AB32" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4953,16 +4941,16 @@
         <v>1</v>
       </c>
       <c r="AH32" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="AI32" t="n">
         <v>3</v>
       </c>
       <c r="AJ32" t="n">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AK32" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AL32" t="n">
         <v>308</v>
@@ -5033,19 +5021,19 @@
         <v>100</v>
       </c>
       <c r="N33" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="O33" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="P33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -5057,31 +5045,31 @@
         <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="Y33" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="Z33" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AA33" t="n">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="AB33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD33" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -5093,16 +5081,16 @@
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AK33" t="n">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="AL33" t="n">
         <v>365</v>
@@ -5173,16 +5161,16 @@
         <v>50</v>
       </c>
       <c r="N34" t="n">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="O34" t="n">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -5197,28 +5185,28 @@
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="Y34" t="n">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="Z34" t="n">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="AA34" t="n">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="AB34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -5233,16 +5221,16 @@
         <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="AK34" t="n">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="AL34" t="n">
         <v>410</v>
@@ -5313,13 +5301,13 @@
         <v>60</v>
       </c>
       <c r="N35" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="O35" t="n">
         <v>182</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q35" t="n">
         <v>0</v>
@@ -5343,19 +5331,19 @@
         <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Y35" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="Z35" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="AA35" t="n">
         <v>182</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
@@ -5379,10 +5367,10 @@
         <v>1</v>
       </c>
       <c r="AJ35" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AK35" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="AL35" t="n">
         <v>303</v>
@@ -5453,13 +5441,13 @@
         <v>80</v>
       </c>
       <c r="N36" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="O36" t="n">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="P36" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -5483,19 +5471,19 @@
         <v>7</v>
       </c>
       <c r="X36" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="Y36" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="Z36" t="n">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="AA36" t="n">
-        <v>217</v>
+        <v>246</v>
       </c>
       <c r="AB36" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
@@ -5519,10 +5507,10 @@
         <v>7</v>
       </c>
       <c r="AJ36" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AK36" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="AL36" t="n">
         <v>412</v>
@@ -5593,16 +5581,16 @@
         <v>80</v>
       </c>
       <c r="N37" t="n">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="O37" t="n">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="P37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -5617,28 +5605,28 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="Y37" t="n">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="Z37" t="n">
-        <v>114</v>
+        <v>96</v>
       </c>
       <c r="AA37" t="n">
-        <v>276</v>
+        <v>318</v>
       </c>
       <c r="AB37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5653,16 +5641,16 @@
         <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="AK37" t="n">
-        <v>352</v>
+        <v>392</v>
       </c>
       <c r="AL37" t="n">
         <v>371</v>
@@ -5733,19 +5721,19 @@
         <v>110</v>
       </c>
       <c r="N38" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="O38" t="n">
-        <v>194</v>
+        <v>228</v>
       </c>
       <c r="P38" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="Q38" t="n">
         <v>2</v>
       </c>
       <c r="R38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -5763,25 +5751,25 @@
         <v>4</v>
       </c>
       <c r="X38" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="Y38" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="Z38" t="n">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="AA38" t="n">
-        <v>194</v>
+        <v>225</v>
       </c>
       <c r="AB38" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="AC38" t="n">
         <v>2</v>
       </c>
       <c r="AD38" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE38" t="n">
         <v>0</v>
@@ -5799,10 +5787,10 @@
         <v>4</v>
       </c>
       <c r="AJ38" t="n">
-        <v>495</v>
+        <v>500</v>
       </c>
       <c r="AK38" t="n">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AL38" t="n">
         <v>453</v>
@@ -5873,22 +5861,22 @@
         <v>50</v>
       </c>
       <c r="N39" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="O39" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="P39" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="Q39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R39" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
         <v>1</v>
@@ -5906,25 +5894,25 @@
         <v>474</v>
       </c>
       <c r="Y39" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="Z39" t="n">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="AA39" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AB39" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="AC39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD39" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AE39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
         <v>1</v>
@@ -5942,7 +5930,7 @@
         <v>474</v>
       </c>
       <c r="AK39" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="AL39" t="n">
         <v>445</v>
@@ -6013,19 +6001,19 @@
         <v>40</v>
       </c>
       <c r="N40" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="O40" t="n">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="P40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -6043,25 +6031,25 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="Y40" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="Z40" t="n">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="AA40" t="n">
-        <v>251</v>
+        <v>273</v>
       </c>
       <c r="AB40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
         <v>0</v>
@@ -6079,10 +6067,10 @@
         <v>0</v>
       </c>
       <c r="AJ40" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AK40" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AL40" t="n">
         <v>379</v>
@@ -6153,13 +6141,13 @@
         <v>110</v>
       </c>
       <c r="N41" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="O41" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="P41" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -6183,19 +6171,19 @@
         <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Y41" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="Z41" t="n">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AA41" t="n">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="AB41" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AC41" t="n">
         <v>0</v>
@@ -6219,10 +6207,10 @@
         <v>1</v>
       </c>
       <c r="AJ41" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AK41" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="AL41" t="n">
         <v>335</v>
@@ -6293,16 +6281,16 @@
         <v>120</v>
       </c>
       <c r="N42" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="O42" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="P42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -6317,28 +6305,28 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X42" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Y42" t="n">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="Z42" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="AA42" t="n">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="AB42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6353,16 +6341,16 @@
         <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ42" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AK42" t="n">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="AL42" t="n">
         <v>371</v>
@@ -6433,19 +6421,19 @@
         <v>60</v>
       </c>
       <c r="N43" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="O43" t="n">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="P43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -6463,25 +6451,25 @@
         <v>1</v>
       </c>
       <c r="X43" t="n">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="Y43" t="n">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="Z43" t="n">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="AA43" t="n">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="AB43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
         <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE43" t="n">
         <v>0</v>
@@ -6499,10 +6487,10 @@
         <v>1</v>
       </c>
       <c r="AJ43" t="n">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="AK43" t="n">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="AL43" t="n">
         <v>331</v>
@@ -6573,19 +6561,19 @@
         <v>100</v>
       </c>
       <c r="N44" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="O44" t="n">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="P44" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -6603,25 +6591,25 @@
         <v>3</v>
       </c>
       <c r="X44" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="Y44" t="n">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="Z44" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="AA44" t="n">
-        <v>231</v>
+        <v>259</v>
       </c>
       <c r="AB44" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
         <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
         <v>0</v>
@@ -6639,10 +6627,10 @@
         <v>3</v>
       </c>
       <c r="AJ44" t="n">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AK44" t="n">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="AL44" t="n">
         <v>301</v>
@@ -6713,16 +6701,16 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="O45" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="P45" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="Q45" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R45" t="n">
         <v>87</v>
@@ -6743,22 +6731,22 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="Y45" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="Z45" t="n">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="AA45" t="n">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="AB45" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AC45" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6779,10 +6767,10 @@
         <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="AK45" t="n">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="AL45" t="n">
         <v>355</v>
@@ -6853,13 +6841,13 @@
         <v>90</v>
       </c>
       <c r="N46" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="O46" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P46" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="Q46" t="n">
         <v>2</v>
@@ -6877,25 +6865,25 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W46" t="n">
         <v>6</v>
       </c>
       <c r="X46" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Y46" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="Z46" t="n">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="AA46" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AB46" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="AC46" t="n">
         <v>2</v>
@@ -6913,16 +6901,16 @@
         <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AI46" t="n">
         <v>6</v>
       </c>
       <c r="AJ46" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AK46" t="n">
-        <v>242</v>
+        <v>256</v>
       </c>
       <c r="AL46" t="n">
         <v>434</v>
@@ -6996,13 +6984,13 @@
         <v>170</v>
       </c>
       <c r="O47" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -7017,28 +7005,28 @@
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="W47" t="n">
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="Y47" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="Z47" t="n">
         <v>170</v>
       </c>
       <c r="AA47" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -7053,16 +7041,16 @@
         <v>0</v>
       </c>
       <c r="AH47" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
       </c>
       <c r="AJ47" t="n">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="AK47" t="n">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AL47" t="n">
         <v>375</v>
@@ -7133,19 +7121,19 @@
         <v>50</v>
       </c>
       <c r="N48" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="O48" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="P48" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Q48" t="n">
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -7157,31 +7145,31 @@
         <v>0</v>
       </c>
       <c r="V48" t="n">
+        <v>41</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>414</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>200</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>213</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>134</v>
+      </c>
+      <c r="AB48" t="n">
         <v>24</v>
       </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>413</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>192</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>220</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>145</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>22</v>
-      </c>
       <c r="AC48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
         <v>0</v>
@@ -7193,16 +7181,16 @@
         <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="AI48" t="n">
         <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AK48" t="n">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="AL48" t="n">
         <v>363</v>
@@ -7276,7 +7264,7 @@
         <v>211</v>
       </c>
       <c r="O49" t="n">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -7285,7 +7273,7 @@
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -7297,7 +7285,7 @@
         <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="W49" t="n">
         <v>0</v>
@@ -7312,10 +7300,10 @@
         <v>211</v>
       </c>
       <c r="AA49" t="n">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="AB49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
         <v>0</v>
@@ -7333,7 +7321,7 @@
         <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="AI49" t="n">
         <v>0</v>
@@ -7413,19 +7401,19 @@
         <v>140</v>
       </c>
       <c r="N50" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O50" t="n">
         <v>192</v>
       </c>
       <c r="P50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -7437,7 +7425,7 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="W50" t="n">
         <v>2</v>
@@ -7446,22 +7434,22 @@
         <v>450</v>
       </c>
       <c r="Y50" t="n">
+        <v>226</v>
+      </c>
+      <c r="Z50" t="n">
         <v>224</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>226</v>
       </c>
       <c r="AA50" t="n">
         <v>192</v>
       </c>
       <c r="AB50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC50" t="n">
         <v>0</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE50" t="n">
         <v>0</v>
@@ -7473,7 +7461,7 @@
         <v>0</v>
       </c>
       <c r="AH50" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AI50" t="n">
         <v>2</v>
@@ -7482,7 +7470,7 @@
         <v>450</v>
       </c>
       <c r="AK50" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AL50" t="n">
         <v>372</v>
@@ -7553,19 +7541,19 @@
         <v>110</v>
       </c>
       <c r="N51" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="O51" t="n">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="P51" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -7577,31 +7565,31 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="W51" t="n">
         <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="Y51" t="n">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="Z51" t="n">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="AA51" t="n">
-        <v>368</v>
+        <v>346</v>
       </c>
       <c r="AB51" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="AC51" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AD51" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AE51" t="n">
         <v>0</v>
@@ -7613,16 +7601,16 @@
         <v>0</v>
       </c>
       <c r="AH51" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="AI51" t="n">
         <v>0</v>
       </c>
       <c r="AJ51" t="n">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AK51" t="n">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="AL51" t="n">
         <v>395</v>
@@ -7693,13 +7681,13 @@
         <v>60</v>
       </c>
       <c r="N52" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="O52" t="n">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="P52" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -7717,25 +7705,25 @@
         <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="W52" t="n">
         <v>1</v>
       </c>
       <c r="X52" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="Y52" t="n">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="Z52" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="AA52" t="n">
-        <v>214</v>
+        <v>247</v>
       </c>
       <c r="AB52" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AC52" t="n">
         <v>0</v>
@@ -7753,16 +7741,16 @@
         <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AI52" t="n">
         <v>1</v>
       </c>
       <c r="AJ52" t="n">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AK52" t="n">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="AL52" t="n">
         <v>378</v>
@@ -7833,16 +7821,16 @@
         <v>90</v>
       </c>
       <c r="N53" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="O53" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="P53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -7863,19 +7851,19 @@
         <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Y53" t="n">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="Z53" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="AA53" t="n">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AB53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC53" t="n">
         <v>5</v>
@@ -7899,10 +7887,10 @@
         <v>0</v>
       </c>
       <c r="AJ53" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AK53" t="n">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="AL53" t="n">
         <v>429</v>
@@ -7973,16 +7961,16 @@
         <v>10</v>
       </c>
       <c r="N54" t="n">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="O54" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R54" t="n">
         <v>22</v>
@@ -8006,19 +7994,19 @@
         <v>424</v>
       </c>
       <c r="Y54" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="Z54" t="n">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="AA54" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AB54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC54" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AD54" t="n">
         <v>22</v>
@@ -8042,7 +8030,7 @@
         <v>424</v>
       </c>
       <c r="AK54" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="AL54" t="n">
         <v>396</v>
@@ -8113,25 +8101,25 @@
         <v>50</v>
       </c>
       <c r="N55" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="O55" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="P55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
         <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -8146,28 +8134,28 @@
         <v>374</v>
       </c>
       <c r="Y55" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Z55" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AA55" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AB55" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
         <v>1</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -8182,7 +8170,7 @@
         <v>374</v>
       </c>
       <c r="AK55" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL55" t="n">
         <v>279</v>
@@ -8253,19 +8241,19 @@
         <v>80</v>
       </c>
       <c r="N56" t="n">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="O56" t="n">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="R56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -8277,31 +8265,31 @@
         <v>0</v>
       </c>
       <c r="V56" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="W56" t="n">
         <v>1</v>
       </c>
       <c r="X56" t="n">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="Y56" t="n">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="Z56" t="n">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="AA56" t="n">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="AB56" t="n">
         <v>0</v>
       </c>
       <c r="AC56" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AD56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE56" t="n">
         <v>0</v>
@@ -8313,16 +8301,16 @@
         <v>0</v>
       </c>
       <c r="AH56" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AI56" t="n">
         <v>1</v>
       </c>
       <c r="AJ56" t="n">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="AK56" t="n">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="AL56" t="n">
         <v>420</v>
@@ -8393,16 +8381,16 @@
         <v>80</v>
       </c>
       <c r="N57" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="O57" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="P57" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R57" t="n">
         <v>1</v>
@@ -8417,28 +8405,28 @@
         <v>0</v>
       </c>
       <c r="V57" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="W57" t="n">
         <v>0</v>
       </c>
       <c r="X57" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="Y57" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="Z57" t="n">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AA57" t="n">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="AB57" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AC57" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD57" t="n">
         <v>1</v>
@@ -8453,16 +8441,16 @@
         <v>0</v>
       </c>
       <c r="AH57" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI57" t="n">
         <v>0</v>
       </c>
       <c r="AJ57" t="n">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="AK57" t="n">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="AL57" t="n">
         <v>336</v>
@@ -8533,22 +8521,22 @@
         <v>110</v>
       </c>
       <c r="N58" t="n">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="O58" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="P58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="Q58" t="n">
         <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T58" t="n">
         <v>0</v>
@@ -8557,34 +8545,34 @@
         <v>0</v>
       </c>
       <c r="V58" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="W58" t="n">
         <v>2</v>
       </c>
       <c r="X58" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="Y58" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="Z58" t="n">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="AA58" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AB58" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AC58" t="n">
         <v>0</v>
       </c>
       <c r="AD58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
         <v>0</v>
@@ -8593,16 +8581,16 @@
         <v>0</v>
       </c>
       <c r="AH58" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AI58" t="n">
         <v>2</v>
       </c>
       <c r="AJ58" t="n">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AK58" t="n">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="AL58" t="n">
         <v>363</v>
@@ -8673,16 +8661,16 @@
         <v>310</v>
       </c>
       <c r="N59" t="n">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="O59" t="n">
         <v>153</v>
       </c>
       <c r="P59" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Q59" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -8703,22 +8691,22 @@
         <v>4</v>
       </c>
       <c r="X59" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Y59" t="n">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="Z59" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="AA59" t="n">
         <v>153</v>
       </c>
       <c r="AB59" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="AC59" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AD59" t="n">
         <v>0</v>
@@ -8739,10 +8727,10 @@
         <v>4</v>
       </c>
       <c r="AJ59" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AK59" t="n">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="AL59" t="n">
         <v>383</v>
@@ -8813,76 +8801,76 @@
         <v>20</v>
       </c>
       <c r="N60" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="O60" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="P60" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="Q60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R60" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="S60" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
       </c>
       <c r="V60" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="W60" t="n">
         <v>0</v>
       </c>
       <c r="X60" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Y60" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="Z60" t="n">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="AA60" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="AB60" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AC60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AD60" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AE60" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
       </c>
       <c r="AH60" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AI60" t="n">
         <v>0</v>
       </c>
       <c r="AJ60" t="n">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AK60" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AL60" t="n">
         <v>377</v>
@@ -9093,22 +9081,22 @@
         <v>90</v>
       </c>
       <c r="N62" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="O62" t="n">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="P62" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
         <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
         <v>0</v>
@@ -9123,28 +9111,28 @@
         <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="Y62" t="n">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="Z62" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="AA62" t="n">
-        <v>247</v>
+        <v>296</v>
       </c>
       <c r="AB62" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
         <v>1</v>
       </c>
       <c r="AD62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
         <v>0</v>
@@ -9159,10 +9147,10 @@
         <v>0</v>
       </c>
       <c r="AJ62" t="n">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="AK62" t="n">
-        <v>334</v>
+        <v>354</v>
       </c>
       <c r="AL62" t="n">
         <v>365</v>
@@ -9233,13 +9221,13 @@
         <v>200</v>
       </c>
       <c r="N63" t="n">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="O63" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="P63" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -9263,19 +9251,19 @@
         <v>0</v>
       </c>
       <c r="X63" t="n">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="Y63" t="n">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="Z63" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="AA63" t="n">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="AB63" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AC63" t="n">
         <v>0</v>
@@ -9299,10 +9287,10 @@
         <v>0</v>
       </c>
       <c r="AJ63" t="n">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="AK63" t="n">
-        <v>284</v>
+        <v>303</v>
       </c>
       <c r="AL63" t="n">
         <v>324</v>
@@ -9373,19 +9361,19 @@
         <v>40</v>
       </c>
       <c r="N64" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="O64" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -9403,16 +9391,16 @@
         <v>2</v>
       </c>
       <c r="X64" t="n">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="Y64" t="n">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="Z64" t="n">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="AA64" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="AB64" t="n">
         <v>0</v>
@@ -9421,7 +9409,7 @@
         <v>0</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE64" t="n">
         <v>0</v>
@@ -9439,10 +9427,10 @@
         <v>2</v>
       </c>
       <c r="AJ64" t="n">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AK64" t="n">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="AL64" t="n">
         <v>440</v>
@@ -9513,19 +9501,19 @@
         <v>180</v>
       </c>
       <c r="N65" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="O65" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="P65" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -9543,25 +9531,25 @@
         <v>0</v>
       </c>
       <c r="X65" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Y65" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Z65" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AA65" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="AB65" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="AC65" t="n">
         <v>0</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE65" t="n">
         <v>0</v>
@@ -9579,10 +9567,10 @@
         <v>0</v>
       </c>
       <c r="AJ65" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AK65" t="n">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AL65" t="n">
         <v>417</v>
@@ -9653,19 +9641,19 @@
         <v>60</v>
       </c>
       <c r="N66" t="n">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="O66" t="n">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="P66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q66" t="n">
         <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -9680,28 +9668,28 @@
         <v>21</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X66" t="n">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="Y66" t="n">
-        <v>240</v>
+        <v>282</v>
       </c>
       <c r="Z66" t="n">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="AA66" t="n">
-        <v>215</v>
+        <v>253</v>
       </c>
       <c r="AB66" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="AC66" t="n">
         <v>0</v>
       </c>
       <c r="AD66" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE66" t="n">
         <v>0</v>
@@ -9719,10 +9707,10 @@
         <v>1</v>
       </c>
       <c r="AJ66" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AK66" t="n">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="AL66" t="n">
         <v>384</v>
@@ -9793,19 +9781,19 @@
         <v>10</v>
       </c>
       <c r="N67" t="n">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="O67" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="P67" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -9823,25 +9811,25 @@
         <v>5</v>
       </c>
       <c r="X67" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="Y67" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="Z67" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="AA67" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="AB67" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="AC67" t="n">
         <v>0</v>
       </c>
       <c r="AD67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AE67" t="n">
         <v>0</v>
@@ -9859,10 +9847,10 @@
         <v>5</v>
       </c>
       <c r="AJ67" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="AK67" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="AL67" t="n">
         <v>297</v>
@@ -9933,19 +9921,19 @@
         <v>100</v>
       </c>
       <c r="N68" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="O68" t="n">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="P68" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="Q68" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -9957,31 +9945,31 @@
         <v>0</v>
       </c>
       <c r="V68" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="W68" t="n">
         <v>0</v>
       </c>
       <c r="X68" t="n">
-        <v>506</v>
+        <v>516</v>
       </c>
       <c r="Y68" t="n">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="Z68" t="n">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="AA68" t="n">
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="AB68" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="AC68" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE68" t="n">
         <v>0</v>
@@ -9993,16 +9981,16 @@
         <v>0</v>
       </c>
       <c r="AH68" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AI68" t="n">
         <v>0</v>
       </c>
       <c r="AJ68" t="n">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="AK68" t="n">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="AL68" t="n">
         <v>395</v>
@@ -10073,19 +10061,19 @@
         <v>100</v>
       </c>
       <c r="N69" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="O69" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="P69" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Q69" t="n">
         <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -10097,31 +10085,31 @@
         <v>0</v>
       </c>
       <c r="V69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W69" t="n">
         <v>0</v>
       </c>
       <c r="X69" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="Y69" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Z69" t="n">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AA69" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="AB69" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="AC69" t="n">
         <v>1</v>
       </c>
       <c r="AD69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE69" t="n">
         <v>0</v>
@@ -10133,16 +10121,16 @@
         <v>0</v>
       </c>
       <c r="AH69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI69" t="n">
         <v>0</v>
       </c>
       <c r="AJ69" t="n">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AK69" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="AL69" t="n">
         <v>317</v>
@@ -10213,19 +10201,19 @@
         <v>20</v>
       </c>
       <c r="N70" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="O70" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -10246,22 +10234,22 @@
         <v>346</v>
       </c>
       <c r="Y70" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="Z70" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AA70" t="n">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AB70" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC70" t="n">
         <v>0</v>
       </c>
       <c r="AD70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE70" t="n">
         <v>0</v>
@@ -10282,7 +10270,7 @@
         <v>346</v>
       </c>
       <c r="AK70" t="n">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AL70" t="n">
         <v>306</v>
@@ -10353,16 +10341,16 @@
         <v>210</v>
       </c>
       <c r="N71" t="n">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="O71" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="P71" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="Q71" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -10383,22 +10371,22 @@
         <v>1</v>
       </c>
       <c r="X71" t="n">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="Y71" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="Z71" t="n">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="AA71" t="n">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="AB71" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AC71" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="AD71" t="n">
         <v>0</v>
@@ -10419,10 +10407,10 @@
         <v>1</v>
       </c>
       <c r="AJ71" t="n">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="AK71" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="AL71" t="n">
         <v>366</v>
@@ -10493,16 +10481,16 @@
         <v>570</v>
       </c>
       <c r="N72" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="O72" t="n">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="P72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
         <v>0</v>
@@ -10523,22 +10511,22 @@
         <v>0</v>
       </c>
       <c r="X72" t="n">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="Y72" t="n">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="Z72" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="AA72" t="n">
-        <v>411</v>
+        <v>451</v>
       </c>
       <c r="AB72" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD72" t="n">
         <v>0</v>
@@ -10559,10 +10547,10 @@
         <v>0</v>
       </c>
       <c r="AJ72" t="n">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="AK72" t="n">
-        <v>465</v>
+        <v>502</v>
       </c>
       <c r="AL72" t="n">
         <v>353</v>
@@ -10633,10 +10621,10 @@
         <v>220</v>
       </c>
       <c r="N73" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="O73" t="n">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="P73" t="n">
         <v>0</v>
@@ -10657,22 +10645,22 @@
         <v>0</v>
       </c>
       <c r="V73" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="W73" t="n">
         <v>1</v>
       </c>
       <c r="X73" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="Y73" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="Z73" t="n">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AA73" t="n">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AB73" t="n">
         <v>0</v>
@@ -10693,16 +10681,16 @@
         <v>0</v>
       </c>
       <c r="AH73" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="AI73" t="n">
         <v>1</v>
       </c>
       <c r="AJ73" t="n">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AK73" t="n">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AL73" t="n">
         <v>362</v>
@@ -10773,16 +10761,16 @@
         <v>40</v>
       </c>
       <c r="N74" t="n">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="O74" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="P74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="R74" t="n">
         <v>0</v>
@@ -10797,28 +10785,28 @@
         <v>0</v>
       </c>
       <c r="V74" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="W74" t="n">
         <v>1</v>
       </c>
       <c r="X74" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Y74" t="n">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="Z74" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AA74" t="n">
-        <v>286</v>
+        <v>312</v>
       </c>
       <c r="AB74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC74" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="AD74" t="n">
         <v>0</v>
@@ -10833,16 +10821,16 @@
         <v>0</v>
       </c>
       <c r="AH74" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AI74" t="n">
         <v>1</v>
       </c>
       <c r="AJ74" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AK74" t="n">
-        <v>351</v>
+        <v>377</v>
       </c>
       <c r="AL74" t="n">
         <v>398</v>
@@ -10913,55 +10901,55 @@
         <v>60</v>
       </c>
       <c r="N75" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O75" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="P75" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>31</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>413</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>251</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>161</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>214</v>
+      </c>
+      <c r="AB75" t="n">
         <v>4</v>
       </c>
-      <c r="Q75" t="n">
-        <v>3</v>
-      </c>
-      <c r="R75" t="n">
-        <v>9</v>
-      </c>
-      <c r="S75" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" t="n">
-        <v>0</v>
-      </c>
-      <c r="U75" t="n">
-        <v>0</v>
-      </c>
-      <c r="V75" t="n">
-        <v>30</v>
-      </c>
-      <c r="W75" t="n">
-        <v>0</v>
-      </c>
-      <c r="X75" t="n">
-        <v>411</v>
-      </c>
-      <c r="Y75" t="n">
-        <v>245</v>
-      </c>
-      <c r="Z75" t="n">
-        <v>164</v>
-      </c>
-      <c r="AA75" t="n">
-        <v>202</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>3</v>
-      </c>
       <c r="AC75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD75" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AE75" t="n">
         <v>0</v>
@@ -10973,16 +10961,16 @@
         <v>0</v>
       </c>
       <c r="AH75" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AI75" t="n">
         <v>0</v>
       </c>
       <c r="AJ75" t="n">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AK75" t="n">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="AL75" t="n">
         <v>359</v>
@@ -11053,13 +11041,13 @@
         <v>10</v>
       </c>
       <c r="N76" t="n">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="O76" t="n">
         <v>133</v>
       </c>
       <c r="P76" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="Q76" t="n">
         <v>0</v>
@@ -11083,19 +11071,19 @@
         <v>0</v>
       </c>
       <c r="X76" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="Y76" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="Z76" t="n">
-        <v>240</v>
+        <v>217</v>
       </c>
       <c r="AA76" t="n">
         <v>133</v>
       </c>
       <c r="AB76" t="n">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="AC76" t="n">
         <v>0</v>
@@ -11119,10 +11107,10 @@
         <v>0</v>
       </c>
       <c r="AJ76" t="n">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="AK76" t="n">
-        <v>168</v>
+        <v>197</v>
       </c>
       <c r="AL76" t="n">
         <v>357</v>
@@ -11193,19 +11181,19 @@
         <v>120</v>
       </c>
       <c r="N77" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="O77" t="n">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="P77" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -11217,31 +11205,31 @@
         <v>0</v>
       </c>
       <c r="V77" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="W77" t="n">
         <v>0</v>
       </c>
       <c r="X77" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="Y77" t="n">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="Z77" t="n">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="AA77" t="n">
-        <v>240</v>
+        <v>296</v>
       </c>
       <c r="AB77" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AC77" t="n">
         <v>9</v>
       </c>
       <c r="AD77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE77" t="n">
         <v>0</v>
@@ -11253,16 +11241,16 @@
         <v>0</v>
       </c>
       <c r="AH77" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="AI77" t="n">
         <v>0</v>
       </c>
       <c r="AJ77" t="n">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AK77" t="n">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="AL77" t="n">
         <v>386</v>
@@ -11333,19 +11321,19 @@
         <v>80</v>
       </c>
       <c r="N78" t="n">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="O78" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="P78" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Q78" t="n">
         <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -11357,31 +11345,31 @@
         <v>0</v>
       </c>
       <c r="V78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W78" t="n">
         <v>1</v>
       </c>
       <c r="X78" t="n">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="Y78" t="n">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="Z78" t="n">
         <v>150</v>
       </c>
       <c r="AA78" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="AB78" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="AC78" t="n">
         <v>0</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE78" t="n">
         <v>0</v>
@@ -11393,16 +11381,16 @@
         <v>0</v>
       </c>
       <c r="AH78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI78" t="n">
         <v>1</v>
       </c>
       <c r="AJ78" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="AK78" t="n">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AL78" t="n">
         <v>350</v>
@@ -11473,13 +11461,13 @@
         <v>80</v>
       </c>
       <c r="N79" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="O79" t="n">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="P79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -11503,19 +11491,19 @@
         <v>0</v>
       </c>
       <c r="X79" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Y79" t="n">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="Z79" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="AA79" t="n">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="AB79" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC79" t="n">
         <v>0</v>
@@ -11539,10 +11527,10 @@
         <v>0</v>
       </c>
       <c r="AJ79" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AK79" t="n">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="AL79" t="n">
         <v>319</v>
@@ -11616,7 +11604,7 @@
         <v>96</v>
       </c>
       <c r="O80" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P80" t="n">
         <v>0</v>
@@ -11625,7 +11613,7 @@
         <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -11652,7 +11640,7 @@
         <v>96</v>
       </c>
       <c r="AA80" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AB80" t="n">
         <v>0</v>
@@ -11661,7 +11649,7 @@
         <v>0</v>
       </c>
       <c r="AD80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE80" t="n">
         <v>0</v>
@@ -11893,19 +11881,19 @@
         <v>50</v>
       </c>
       <c r="N82" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="O82" t="n">
         <v>218</v>
       </c>
       <c r="P82" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q82" t="n">
         <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -11923,25 +11911,25 @@
         <v>0</v>
       </c>
       <c r="X82" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="Y82" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="Z82" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="AA82" t="n">
         <v>218</v>
       </c>
       <c r="AB82" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AC82" t="n">
         <v>0</v>
       </c>
       <c r="AD82" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE82" t="n">
         <v>0</v>
@@ -11959,10 +11947,10 @@
         <v>0</v>
       </c>
       <c r="AJ82" t="n">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="AK82" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="AL82" t="n">
         <v>385</v>
@@ -12033,19 +12021,19 @@
         <v>110</v>
       </c>
       <c r="N83" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="O83" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="P83" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Q83" t="n">
         <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -12063,25 +12051,25 @@
         <v>0</v>
       </c>
       <c r="X83" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="Y83" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="Z83" t="n">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AA83" t="n">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="AB83" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AC83" t="n">
         <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AE83" t="n">
         <v>0</v>
@@ -12099,10 +12087,10 @@
         <v>0</v>
       </c>
       <c r="AJ83" t="n">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AK83" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="AL83" t="n">
         <v>340</v>
@@ -12173,16 +12161,16 @@
         <v>20</v>
       </c>
       <c r="N84" t="n">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="O84" t="n">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="P84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="R84" t="n">
         <v>0</v>
@@ -12197,28 +12185,28 @@
         <v>0</v>
       </c>
       <c r="V84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W84" t="n">
         <v>0</v>
       </c>
       <c r="X84" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Y84" t="n">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="Z84" t="n">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="AA84" t="n">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="AB84" t="n">
         <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AD84" t="n">
         <v>0</v>
@@ -12233,16 +12221,16 @@
         <v>0</v>
       </c>
       <c r="AH84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AI84" t="n">
         <v>0</v>
       </c>
       <c r="AJ84" t="n">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AK84" t="n">
-        <v>225</v>
+        <v>253</v>
       </c>
       <c r="AL84" t="n">
         <v>378</v>
@@ -12313,13 +12301,13 @@
         <v>50</v>
       </c>
       <c r="N85" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="O85" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="P85" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q85" t="n">
         <v>0</v>
@@ -12337,25 +12325,25 @@
         <v>0</v>
       </c>
       <c r="V85" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="W85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="Y85" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="Z85" t="n">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="AA85" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="AB85" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC85" t="n">
         <v>0</v>
@@ -12373,16 +12361,16 @@
         <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AI85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ85" t="n">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AK85" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AL85" t="n">
         <v>367</v>
@@ -12453,22 +12441,22 @@
         <v>40</v>
       </c>
       <c r="N86" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O86" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="P86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="R86" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="S86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T86" t="n">
         <v>0</v>
@@ -12477,7 +12465,7 @@
         <v>0</v>
       </c>
       <c r="V86" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="W86" t="n">
         <v>0</v>
@@ -12486,25 +12474,25 @@
         <v>447</v>
       </c>
       <c r="Y86" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="Z86" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AA86" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="AB86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC86" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AD86" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="AE86" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF86" t="n">
         <v>0</v>
@@ -12513,7 +12501,7 @@
         <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -12522,7 +12510,7 @@
         <v>447</v>
       </c>
       <c r="AK86" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="AL86" t="n">
         <v>367</v>
@@ -12593,16 +12581,16 @@
         <v>60</v>
       </c>
       <c r="N87" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="O87" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q87" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="R87" t="n">
         <v>27</v>
@@ -12617,28 +12605,28 @@
         <v>0</v>
       </c>
       <c r="V87" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="W87" t="n">
         <v>0</v>
       </c>
       <c r="X87" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="Y87" t="n">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="Z87" t="n">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="AA87" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AB87" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AC87" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AD87" t="n">
         <v>27</v>
@@ -12653,16 +12641,16 @@
         <v>0</v>
       </c>
       <c r="AH87" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
       </c>
       <c r="AJ87" t="n">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AK87" t="n">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="AL87" t="n">
         <v>360</v>
@@ -12733,16 +12721,16 @@
         <v>60</v>
       </c>
       <c r="N88" t="n">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="O88" t="n">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="P88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q88" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R88" t="n">
         <v>1</v>
@@ -12757,28 +12745,28 @@
         <v>0</v>
       </c>
       <c r="V88" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="W88" t="n">
         <v>0</v>
       </c>
       <c r="X88" t="n">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="Y88" t="n">
-        <v>264</v>
+        <v>286</v>
       </c>
       <c r="Z88" t="n">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="AA88" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="AB88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC88" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="AD88" t="n">
         <v>1</v>
@@ -12793,16 +12781,16 @@
         <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
       </c>
       <c r="AJ88" t="n">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="AK88" t="n">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="AL88" t="n">
         <v>356</v>
@@ -12873,19 +12861,19 @@
         <v>170</v>
       </c>
       <c r="N89" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="O89" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="P89" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="Q89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -12897,7 +12885,7 @@
         <v>0</v>
       </c>
       <c r="V89" t="n">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="W89" t="n">
         <v>0</v>
@@ -12906,22 +12894,22 @@
         <v>492</v>
       </c>
       <c r="Y89" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="Z89" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="AA89" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="AB89" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="AC89" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AD89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE89" t="n">
         <v>0</v>
@@ -12933,7 +12921,7 @@
         <v>0</v>
       </c>
       <c r="AH89" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="AI89" t="n">
         <v>0</v>
@@ -12942,7 +12930,7 @@
         <v>492</v>
       </c>
       <c r="AK89" t="n">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AL89" t="n">
         <v>405</v>
@@ -13013,16 +13001,16 @@
         <v>140</v>
       </c>
       <c r="N90" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="O90" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="P90" t="n">
         <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
@@ -13037,28 +13025,28 @@
         <v>0</v>
       </c>
       <c r="V90" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X90" t="n">
         <v>323</v>
       </c>
       <c r="Y90" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="Z90" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="AA90" t="n">
-        <v>125</v>
+        <v>137</v>
       </c>
       <c r="AB90" t="n">
         <v>0</v>
       </c>
       <c r="AC90" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="AD90" t="n">
         <v>0</v>
@@ -13073,16 +13061,16 @@
         <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ90" t="n">
         <v>323</v>
       </c>
       <c r="AK90" t="n">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AL90" t="n">
         <v>301</v>
@@ -13153,13 +13141,13 @@
         <v>60</v>
       </c>
       <c r="N91" t="n">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="O91" t="n">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="P91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q91" t="n">
         <v>0</v>
@@ -13183,19 +13171,19 @@
         <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="Y91" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="Z91" t="n">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="AA91" t="n">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="AB91" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AC91" t="n">
         <v>0</v>
@@ -13219,10 +13207,10 @@
         <v>0</v>
       </c>
       <c r="AJ91" t="n">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="AK91" t="n">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="AL91" t="n">
         <v>399</v>
@@ -13293,13 +13281,13 @@
         <v>140</v>
       </c>
       <c r="N92" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="O92" t="n">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="P92" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
         <v>5</v>
@@ -13323,19 +13311,19 @@
         <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Y92" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="Z92" t="n">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AA92" t="n">
-        <v>213</v>
+        <v>262</v>
       </c>
       <c r="AB92" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="AC92" t="n">
         <v>5</v>
@@ -13359,10 +13347,10 @@
         <v>0</v>
       </c>
       <c r="AJ92" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AK92" t="n">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AL92" t="n">
         <v>364</v>
@@ -13433,10 +13421,10 @@
         <v>30</v>
       </c>
       <c r="N93" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="O93" t="n">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="P93" t="n">
         <v>0</v>
@@ -13445,7 +13433,7 @@
         <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -13463,16 +13451,16 @@
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="Y93" t="n">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="Z93" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="AA93" t="n">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="AB93" t="n">
         <v>0</v>
@@ -13481,7 +13469,7 @@
         <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="n">
         <v>0</v>
@@ -13499,10 +13487,10 @@
         <v>0</v>
       </c>
       <c r="AJ93" t="n">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AK93" t="n">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="AL93" t="n">
         <v>335</v>
@@ -13576,16 +13564,16 @@
         <v>198</v>
       </c>
       <c r="O94" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="P94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -13597,7 +13585,7 @@
         <v>1</v>
       </c>
       <c r="V94" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="W94" t="n">
         <v>0</v>
@@ -13606,22 +13594,22 @@
         <v>408</v>
       </c>
       <c r="Y94" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="Z94" t="n">
         <v>198</v>
       </c>
       <c r="AA94" t="n">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="AB94" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE94" t="n">
         <v>0</v>
@@ -13633,7 +13621,7 @@
         <v>1</v>
       </c>
       <c r="AH94" t="n">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
@@ -13642,7 +13630,7 @@
         <v>408</v>
       </c>
       <c r="AK94" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AL94" t="n">
         <v>373</v>
@@ -13713,19 +13701,19 @@
         <v>70</v>
       </c>
       <c r="N95" t="n">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="O95" t="n">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="P95" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="Q95" t="n">
         <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -13743,25 +13731,25 @@
         <v>0</v>
       </c>
       <c r="X95" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="Y95" t="n">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="Z95" t="n">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="AA95" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="AB95" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AC95" t="n">
         <v>0</v>
       </c>
       <c r="AD95" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE95" t="n">
         <v>0</v>
@@ -13779,10 +13767,10 @@
         <v>0</v>
       </c>
       <c r="AJ95" t="n">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AK95" t="n">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="AL95" t="n">
         <v>356</v>
@@ -13853,19 +13841,19 @@
         <v>70</v>
       </c>
       <c r="N96" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="O96" t="n">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="P96" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
         <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -13883,25 +13871,25 @@
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="Y96" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="Z96" t="n">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="AA96" t="n">
-        <v>188</v>
+        <v>260</v>
       </c>
       <c r="AB96" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="AC96" t="n">
         <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE96" t="n">
         <v>0</v>
@@ -13919,10 +13907,10 @@
         <v>0</v>
       </c>
       <c r="AJ96" t="n">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="AK96" t="n">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="AL96" t="n">
         <v>282</v>
@@ -13993,49 +13981,49 @@
         <v>30</v>
       </c>
       <c r="N97" t="n">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="O97" t="n">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="P97" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Q97" t="n">
         <v>44</v>
       </c>
       <c r="R97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U97" t="n">
         <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="W97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X97" t="n">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="Y97" t="n">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="Z97" t="n">
-        <v>134</v>
+        <v>115</v>
       </c>
       <c r="AA97" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="AB97" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AC97" t="n">
         <v>44</v>
@@ -14047,22 +14035,22 @@
         <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
       </c>
       <c r="AH97" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AI97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ97" t="n">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AK97" t="n">
-        <v>216</v>
+        <v>240</v>
       </c>
       <c r="AL97" t="n">
         <v>378</v>
@@ -14133,19 +14121,19 @@
         <v>30</v>
       </c>
       <c r="N98" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="O98" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="P98" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="Q98" t="n">
         <v>9</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -14166,22 +14154,22 @@
         <v>399</v>
       </c>
       <c r="Y98" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Z98" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AA98" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="AB98" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AC98" t="n">
         <v>9</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -14202,7 +14190,7 @@
         <v>399</v>
       </c>
       <c r="AK98" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AL98" t="n">
         <v>367</v>
@@ -14273,10 +14261,10 @@
         <v>40</v>
       </c>
       <c r="N99" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="O99" t="n">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="P99" t="n">
         <v>0</v>
@@ -14285,7 +14273,7 @@
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -14303,16 +14291,16 @@
         <v>2</v>
       </c>
       <c r="X99" t="n">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="Y99" t="n">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="Z99" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="AA99" t="n">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="AB99" t="n">
         <v>0</v>
@@ -14321,7 +14309,7 @@
         <v>0</v>
       </c>
       <c r="AD99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AE99" t="n">
         <v>0</v>
@@ -14339,10 +14327,10 @@
         <v>2</v>
       </c>
       <c r="AJ99" t="n">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="AK99" t="n">
-        <v>280</v>
+        <v>297</v>
       </c>
       <c r="AL99" t="n">
         <v>321</v>
@@ -14413,19 +14401,19 @@
         <v>80</v>
       </c>
       <c r="N100" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="O100" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="P100" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -14437,31 +14425,31 @@
         <v>0</v>
       </c>
       <c r="V100" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="W100" t="n">
         <v>0</v>
       </c>
       <c r="X100" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="Y100" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="Z100" t="n">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="AA100" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="AB100" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AC100" t="n">
         <v>0</v>
       </c>
       <c r="AD100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE100" t="n">
         <v>0</v>
@@ -14473,16 +14461,16 @@
         <v>0</v>
       </c>
       <c r="AH100" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AI100" t="n">
         <v>0</v>
       </c>
       <c r="AJ100" t="n">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AK100" t="n">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="AL100" t="n">
         <v>343</v>
@@ -14553,58 +14541,58 @@
         <v>120</v>
       </c>
       <c r="N101" t="n">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="O101" t="n">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q101" t="n">
         <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
+        <v>1</v>
+      </c>
+      <c r="U101" t="n">
+        <v>0</v>
+      </c>
+      <c r="V101" t="n">
+        <v>84</v>
+      </c>
+      <c r="W101" t="n">
+        <v>1</v>
+      </c>
+      <c r="X101" t="n">
+        <v>509</v>
+      </c>
+      <c r="Y101" t="n">
+        <v>311</v>
+      </c>
+      <c r="Z101" t="n">
+        <v>199</v>
+      </c>
+      <c r="AA101" t="n">
+        <v>219</v>
+      </c>
+      <c r="AB101" t="n">
         <v>2</v>
       </c>
-      <c r="T101" t="n">
-        <v>1</v>
-      </c>
-      <c r="U101" t="n">
-        <v>0</v>
-      </c>
-      <c r="V101" t="n">
-        <v>82</v>
-      </c>
-      <c r="W101" t="n">
-        <v>1</v>
-      </c>
-      <c r="X101" t="n">
-        <v>502</v>
-      </c>
-      <c r="Y101" t="n">
-        <v>290</v>
-      </c>
-      <c r="Z101" t="n">
-        <v>212</v>
-      </c>
-      <c r="AA101" t="n">
-        <v>203</v>
-      </c>
-      <c r="AB101" t="n">
-        <v>0</v>
-      </c>
       <c r="AC101" t="n">
         <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
         <v>1</v>
@@ -14613,16 +14601,16 @@
         <v>0</v>
       </c>
       <c r="AH101" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AI101" t="n">
         <v>1</v>
       </c>
       <c r="AJ101" t="n">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="AK101" t="n">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="AL101" t="n">
         <v>455</v>
@@ -14693,13 +14681,13 @@
         <v>90</v>
       </c>
       <c r="N102" t="n">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="O102" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="P102" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="Q102" t="n">
         <v>5</v>
@@ -14723,19 +14711,19 @@
         <v>2</v>
       </c>
       <c r="X102" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="Y102" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="Z102" t="n">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="AA102" t="n">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="AB102" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AC102" t="n">
         <v>5</v>
@@ -14759,10 +14747,10 @@
         <v>2</v>
       </c>
       <c r="AJ102" t="n">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AK102" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AL102" t="n">
         <v>472</v>
@@ -14833,10 +14821,10 @@
         <v>60</v>
       </c>
       <c r="N103" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="O103" t="n">
-        <v>322</v>
+        <v>352</v>
       </c>
       <c r="P103" t="n">
         <v>0</v>
@@ -14845,7 +14833,7 @@
         <v>1</v>
       </c>
       <c r="R103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -14863,25 +14851,25 @@
         <v>1</v>
       </c>
       <c r="X103" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="Y103" t="n">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="Z103" t="n">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="AA103" t="n">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="AB103" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC103" t="n">
         <v>1</v>
       </c>
       <c r="AD103" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -14899,10 +14887,10 @@
         <v>1</v>
       </c>
       <c r="AJ103" t="n">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="AK103" t="n">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="AL103" t="n">
         <v>316</v>
@@ -14973,19 +14961,19 @@
         <v>30</v>
       </c>
       <c r="N104" t="n">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O104" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P104" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="Q104" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="R104" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -15003,25 +14991,25 @@
         <v>3</v>
       </c>
       <c r="X104" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="Y104" t="n">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="Z104" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AA104" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AB104" t="n">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="AC104" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AD104" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AE104" t="n">
         <v>0</v>
@@ -15039,10 +15027,10 @@
         <v>3</v>
       </c>
       <c r="AJ104" t="n">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AK104" t="n">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="AL104" t="n">
         <v>422</v>
@@ -15113,16 +15101,16 @@
         <v>70</v>
       </c>
       <c r="N105" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="O105" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="P105" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="Q105" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R105" t="n">
         <v>0</v>
@@ -15143,22 +15131,22 @@
         <v>0</v>
       </c>
       <c r="X105" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="Y105" t="n">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="Z105" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="AA105" t="n">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="AB105" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="AC105" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AD105" t="n">
         <v>0</v>
@@ -15179,10 +15167,10 @@
         <v>0</v>
       </c>
       <c r="AJ105" t="n">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AK105" t="n">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="AL105" t="n">
         <v>391</v>
@@ -15253,10 +15241,10 @@
         <v>130</v>
       </c>
       <c r="N106" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="O106" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="P106" t="n">
         <v>0</v>
@@ -15265,7 +15253,7 @@
         <v>1</v>
       </c>
       <c r="R106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -15277,22 +15265,22 @@
         <v>0</v>
       </c>
       <c r="V106" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="W106" t="n">
         <v>0</v>
       </c>
       <c r="X106" t="n">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="Y106" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="Z106" t="n">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="AA106" t="n">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="AB106" t="n">
         <v>0</v>
@@ -15301,7 +15289,7 @@
         <v>1</v>
       </c>
       <c r="AD106" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE106" t="n">
         <v>0</v>
@@ -15313,16 +15301,16 @@
         <v>0</v>
       </c>
       <c r="AH106" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AI106" t="n">
         <v>0</v>
       </c>
       <c r="AJ106" t="n">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="AK106" t="n">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="AL106" t="n">
         <v>366</v>
@@ -15393,13 +15381,13 @@
         <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="O107" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="P107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Q107" t="n">
         <v>0</v>
@@ -15426,16 +15414,16 @@
         <v>367</v>
       </c>
       <c r="Y107" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="Z107" t="n">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="AA107" t="n">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="AB107" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AC107" t="n">
         <v>0</v>
@@ -15462,7 +15450,7 @@
         <v>367</v>
       </c>
       <c r="AK107" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="AL107" t="n">
         <v>322</v>
@@ -15533,19 +15521,19 @@
         <v>170</v>
       </c>
       <c r="N108" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="O108" t="n">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="P108" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
         <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -15566,22 +15554,22 @@
         <v>382</v>
       </c>
       <c r="Y108" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="Z108" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="AA108" t="n">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="AB108" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC108" t="n">
         <v>0</v>
       </c>
       <c r="AD108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE108" t="n">
         <v>0</v>
@@ -15602,7 +15590,7 @@
         <v>382</v>
       </c>
       <c r="AK108" t="n">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="AL108" t="n">
         <v>324</v>
@@ -15673,19 +15661,19 @@
         <v>70</v>
       </c>
       <c r="N109" t="n">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="O109" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="P109" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="Q109" t="n">
         <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -15697,31 +15685,31 @@
         <v>0</v>
       </c>
       <c r="V109" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="W109" t="n">
         <v>1</v>
       </c>
       <c r="X109" t="n">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="Y109" t="n">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="Z109" t="n">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AA109" t="n">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="AB109" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AC109" t="n">
         <v>0</v>
       </c>
       <c r="AD109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE109" t="n">
         <v>0</v>
@@ -15733,16 +15721,16 @@
         <v>0</v>
       </c>
       <c r="AH109" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="AI109" t="n">
         <v>1</v>
       </c>
       <c r="AJ109" t="n">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="AK109" t="n">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="AL109" t="n">
         <v>407</v>
@@ -15813,19 +15801,19 @@
         <v>220</v>
       </c>
       <c r="N110" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="O110" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="P110" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
         <v>5</v>
       </c>
       <c r="R110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -15840,28 +15828,28 @@
         <v>20</v>
       </c>
       <c r="W110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X110" t="n">
         <v>622</v>
       </c>
       <c r="Y110" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="Z110" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="AA110" t="n">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="AB110" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>5</v>
       </c>
       <c r="AD110" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE110" t="n">
         <v>0</v>
@@ -15876,13 +15864,13 @@
         <v>20</v>
       </c>
       <c r="AI110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ110" t="n">
         <v>622</v>
       </c>
       <c r="AK110" t="n">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="AL110" t="n">
         <v>507</v>
@@ -15953,13 +15941,13 @@
         <v>10</v>
       </c>
       <c r="N111" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="O111" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="P111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q111" t="n">
         <v>2</v>
@@ -15983,19 +15971,19 @@
         <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="Y111" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="Z111" t="n">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="AA111" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="AB111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC111" t="n">
         <v>2</v>
@@ -16019,10 +16007,10 @@
         <v>0</v>
       </c>
       <c r="AJ111" t="n">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="AK111" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="AL111" t="n">
         <v>294</v>
@@ -16093,10 +16081,10 @@
         <v>40</v>
       </c>
       <c r="N112" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="O112" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
@@ -16117,22 +16105,22 @@
         <v>0</v>
       </c>
       <c r="V112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W112" t="n">
         <v>0</v>
       </c>
       <c r="X112" t="n">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="Y112" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="Z112" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AA112" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="AB112" t="n">
         <v>0</v>
@@ -16153,16 +16141,16 @@
         <v>0</v>
       </c>
       <c r="AH112" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AI112" t="n">
         <v>0</v>
       </c>
       <c r="AJ112" t="n">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="AK112" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="AL112" t="n">
         <v>403</v>
@@ -16233,19 +16221,19 @@
         <v>420</v>
       </c>
       <c r="N113" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="O113" t="n">
-        <v>194</v>
+        <v>278</v>
       </c>
       <c r="P113" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="Q113" t="n">
         <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -16257,31 +16245,31 @@
         <v>0</v>
       </c>
       <c r="V113" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="W113" t="n">
         <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="Y113" t="n">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="Z113" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="AA113" t="n">
-        <v>194</v>
+        <v>278</v>
       </c>
       <c r="AB113" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="AC113" t="n">
         <v>0</v>
       </c>
       <c r="AD113" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -16293,16 +16281,16 @@
         <v>0</v>
       </c>
       <c r="AH113" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="AI113" t="n">
         <v>0</v>
       </c>
       <c r="AJ113" t="n">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="AK113" t="n">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="AL113" t="n">
         <v>362</v>
@@ -16376,10 +16364,10 @@
         <v>0</v>
       </c>
       <c r="O114" t="n">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="P114" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="Q114" t="n">
         <v>0</v>
@@ -16397,7 +16385,7 @@
         <v>0</v>
       </c>
       <c r="V114" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="W114" t="n">
         <v>4</v>
@@ -16412,10 +16400,10 @@
         <v>0</v>
       </c>
       <c r="AA114" t="n">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="AB114" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="AC114" t="n">
         <v>0</v>
@@ -16433,7 +16421,7 @@
         <v>0</v>
       </c>
       <c r="AH114" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AI114" t="n">
         <v>4</v>
@@ -16516,7 +16504,7 @@
         <v>212</v>
       </c>
       <c r="O115" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P115" t="n">
         <v>6</v>
@@ -16537,7 +16525,7 @@
         <v>0</v>
       </c>
       <c r="V115" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W115" t="n">
         <v>0</v>
@@ -16552,7 +16540,7 @@
         <v>212</v>
       </c>
       <c r="AA115" t="n">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="AB115" t="n">
         <v>6</v>
@@ -16573,7 +16561,7 @@
         <v>0</v>
       </c>
       <c r="AH115" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI115" t="n">
         <v>0</v>
@@ -16653,13 +16641,13 @@
         <v>110</v>
       </c>
       <c r="N116" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="O116" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="P116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
         <v>0</v>
@@ -16683,19 +16671,19 @@
         <v>1</v>
       </c>
       <c r="X116" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="Y116" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="Z116" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="AA116" t="n">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="AB116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
         <v>0</v>
@@ -16719,10 +16707,10 @@
         <v>1</v>
       </c>
       <c r="AJ116" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AK116" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AL116" t="n">
         <v>333</v>
@@ -16793,19 +16781,19 @@
         <v>80</v>
       </c>
       <c r="N117" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="O117" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="P117" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="Q117" t="n">
         <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -16817,31 +16805,31 @@
         <v>0</v>
       </c>
       <c r="V117" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="W117" t="n">
         <v>0</v>
       </c>
       <c r="X117" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="Y117" t="n">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="Z117" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="AA117" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="AB117" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AC117" t="n">
         <v>0</v>
       </c>
       <c r="AD117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE117" t="n">
         <v>0</v>
@@ -16853,16 +16841,16 @@
         <v>0</v>
       </c>
       <c r="AH117" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AI117" t="n">
         <v>0</v>
       </c>
       <c r="AJ117" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AK117" t="n">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="AL117" t="n">
         <v>364</v>
@@ -16933,16 +16921,16 @@
         <v>50</v>
       </c>
       <c r="N118" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="O118" t="n">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="P118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
         <v>0</v>
@@ -16963,22 +16951,22 @@
         <v>0</v>
       </c>
       <c r="X118" t="n">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="Y118" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="Z118" t="n">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="AA118" t="n">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="AB118" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AC118" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD118" t="n">
         <v>0</v>
@@ -16999,10 +16987,10 @@
         <v>0</v>
       </c>
       <c r="AJ118" t="n">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="AK118" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="AL118" t="n">
         <v>378</v>
@@ -17073,13 +17061,13 @@
         <v>30</v>
       </c>
       <c r="N119" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="O119" t="n">
-        <v>195</v>
+        <v>318</v>
       </c>
       <c r="P119" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
         <v>0</v>
@@ -17103,19 +17091,19 @@
         <v>3</v>
       </c>
       <c r="X119" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Y119" t="n">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="Z119" t="n">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AA119" t="n">
-        <v>195</v>
+        <v>318</v>
       </c>
       <c r="AB119" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="AC119" t="n">
         <v>0</v>
@@ -17139,10 +17127,10 @@
         <v>3</v>
       </c>
       <c r="AJ119" t="n">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AK119" t="n">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="AL119" t="n">
         <v>420</v>
@@ -17213,76 +17201,76 @@
         <v>70</v>
       </c>
       <c r="N120" t="n">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="O120" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P120" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q120" t="n">
+        <v>2</v>
+      </c>
+      <c r="R120" t="n">
+        <v>1</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0</v>
+      </c>
+      <c r="T120" t="n">
         <v>3</v>
       </c>
-      <c r="R120" t="n">
-        <v>0</v>
-      </c>
-      <c r="S120" t="n">
+      <c r="U120" t="n">
+        <v>0</v>
+      </c>
+      <c r="V120" t="n">
+        <v>80</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0</v>
+      </c>
+      <c r="X120" t="n">
+        <v>511</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>273</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>236</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>181</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC120" t="n">
         <v>2</v>
       </c>
-      <c r="T120" t="n">
-        <v>2</v>
-      </c>
-      <c r="U120" t="n">
-        <v>0</v>
-      </c>
-      <c r="V120" t="n">
-        <v>56</v>
-      </c>
-      <c r="W120" t="n">
-        <v>0</v>
-      </c>
-      <c r="X120" t="n">
-        <v>509</v>
-      </c>
-      <c r="Y120" t="n">
-        <v>250</v>
-      </c>
-      <c r="Z120" t="n">
-        <v>254</v>
-      </c>
-      <c r="AA120" t="n">
-        <v>169</v>
-      </c>
-      <c r="AB120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC120" t="n">
+      <c r="AD120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="n">
         <v>3</v>
       </c>
-      <c r="AD120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE120" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF120" t="n">
-        <v>2</v>
-      </c>
       <c r="AG120" t="n">
         <v>0</v>
       </c>
       <c r="AH120" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AI120" t="n">
         <v>0</v>
       </c>
       <c r="AJ120" t="n">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="AK120" t="n">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="AL120" t="n">
         <v>430</v>
@@ -17353,19 +17341,19 @@
         <v>360</v>
       </c>
       <c r="N121" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="O121" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="P121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q121" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -17377,31 +17365,31 @@
         <v>0</v>
       </c>
       <c r="V121" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="W121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X121" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Y121" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="Z121" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="AA121" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="AB121" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC121" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AD121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -17413,16 +17401,16 @@
         <v>0</v>
       </c>
       <c r="AH121" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AI121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ121" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AK121" t="n">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="AL121" t="n">
         <v>379</v>
@@ -17493,10 +17481,10 @@
         <v>40</v>
       </c>
       <c r="N122" t="n">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="O122" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="P122" t="n">
         <v>2</v>
@@ -17505,7 +17493,7 @@
         <v>1</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -17523,16 +17511,16 @@
         <v>0</v>
       </c>
       <c r="X122" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Y122" t="n">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="Z122" t="n">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="AA122" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
       <c r="AB122" t="n">
         <v>2</v>
@@ -17541,7 +17529,7 @@
         <v>1</v>
       </c>
       <c r="AD122" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -17559,10 +17547,10 @@
         <v>0</v>
       </c>
       <c r="AJ122" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AK122" t="n">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="AL122" t="n">
         <v>419</v>
@@ -17633,13 +17621,13 @@
         <v>100</v>
       </c>
       <c r="N123" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="O123" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="P123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q123" t="n">
         <v>5</v>
@@ -17648,7 +17636,7 @@
         <v>1</v>
       </c>
       <c r="S123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T123" t="n">
         <v>0</v>
@@ -17666,16 +17654,16 @@
         <v>493</v>
       </c>
       <c r="Y123" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="Z123" t="n">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="AA123" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="AB123" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC123" t="n">
         <v>5</v>
@@ -17684,7 +17672,7 @@
         <v>1</v>
       </c>
       <c r="AE123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
         <v>0</v>
@@ -17702,7 +17690,7 @@
         <v>493</v>
       </c>
       <c r="AK123" t="n">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AL123" t="n">
         <v>432</v>
@@ -17773,13 +17761,13 @@
         <v>160</v>
       </c>
       <c r="N124" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="O124" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="P124" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
         <v>4</v>
@@ -17803,19 +17791,19 @@
         <v>1</v>
       </c>
       <c r="X124" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Y124" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Z124" t="n">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="AA124" t="n">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AB124" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC124" t="n">
         <v>4</v>
@@ -17839,10 +17827,10 @@
         <v>1</v>
       </c>
       <c r="AJ124" t="n">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AK124" t="n">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="AL124" t="n">
         <v>437</v>
@@ -17913,19 +17901,19 @@
         <v>170</v>
       </c>
       <c r="N125" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="O125" t="n">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="P125" t="n">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="Q125" t="n">
         <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -17943,25 +17931,25 @@
         <v>2</v>
       </c>
       <c r="X125" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="Y125" t="n">
-        <v>266</v>
+        <v>319</v>
       </c>
       <c r="Z125" t="n">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="AA125" t="n">
-        <v>128</v>
+        <v>225</v>
       </c>
       <c r="AB125" t="n">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="AC125" t="n">
         <v>0</v>
       </c>
       <c r="AD125" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE125" t="n">
         <v>0</v>
@@ -17979,10 +17967,10 @@
         <v>2</v>
       </c>
       <c r="AJ125" t="n">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="AK125" t="n">
-        <v>265</v>
+        <v>319</v>
       </c>
       <c r="AL125" t="n">
         <v>303</v>
@@ -18053,10 +18041,10 @@
         <v>60</v>
       </c>
       <c r="N126" t="n">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="O126" t="n">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="P126" t="n">
         <v>0</v>
@@ -18077,25 +18065,25 @@
         <v>0</v>
       </c>
       <c r="V126" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="W126" t="n">
         <v>0</v>
       </c>
       <c r="X126" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="Y126" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="Z126" t="n">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="AA126" t="n">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="AB126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC126" t="n">
         <v>0</v>
@@ -18113,16 +18101,16 @@
         <v>0</v>
       </c>
       <c r="AH126" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AI126" t="n">
         <v>0</v>
       </c>
       <c r="AJ126" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="AK126" t="n">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="AL126" t="n">
         <v>366</v>
@@ -18193,16 +18181,16 @@
         <v>140</v>
       </c>
       <c r="N127" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="O127" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q127" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="R127" t="n">
         <v>2</v>
@@ -18223,22 +18211,22 @@
         <v>0</v>
       </c>
       <c r="X127" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="Y127" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="Z127" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="AA127" t="n">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC127" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AD127" t="n">
         <v>2</v>
@@ -18259,10 +18247,10 @@
         <v>0</v>
       </c>
       <c r="AJ127" t="n">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AK127" t="n">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="AL127" t="n">
         <v>394</v>
@@ -18336,13 +18324,13 @@
         <v>180</v>
       </c>
       <c r="O128" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="P128" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="Q128" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="R128" t="n">
         <v>2</v>
@@ -18357,7 +18345,7 @@
         <v>0</v>
       </c>
       <c r="V128" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="W128" t="n">
         <v>0</v>
@@ -18366,19 +18354,19 @@
         <v>470</v>
       </c>
       <c r="Y128" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="Z128" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AA128" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="AB128" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AC128" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AD128" t="n">
         <v>2</v>
@@ -18393,7 +18381,7 @@
         <v>0</v>
       </c>
       <c r="AH128" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AI128" t="n">
         <v>0</v>
@@ -18402,7 +18390,7 @@
         <v>470</v>
       </c>
       <c r="AK128" t="n">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="AL128" t="n">
         <v>372</v>
@@ -18473,13 +18461,13 @@
         <v>50</v>
       </c>
       <c r="N129" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="O129" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q129" t="n">
         <v>0</v>
@@ -18506,16 +18494,16 @@
         <v>345</v>
       </c>
       <c r="Y129" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="Z129" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="AA129" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="AB129" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC129" t="n">
         <v>0</v>
@@ -18542,7 +18530,7 @@
         <v>345</v>
       </c>
       <c r="AK129" t="n">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="AL129" t="n">
         <v>313</v>
@@ -18613,19 +18601,19 @@
         <v>40</v>
       </c>
       <c r="N130" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="O130" t="n">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="P130" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -18643,25 +18631,25 @@
         <v>0</v>
       </c>
       <c r="X130" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Y130" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="Z130" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="AA130" t="n">
-        <v>160</v>
+        <v>259</v>
       </c>
       <c r="AB130" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="AC130" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AD130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE130" t="n">
         <v>0</v>
@@ -18679,10 +18667,10 @@
         <v>0</v>
       </c>
       <c r="AJ130" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AK130" t="n">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="AL130" t="n">
         <v>386</v>
@@ -18753,13 +18741,13 @@
         <v>70</v>
       </c>
       <c r="N131" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="O131" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="P131" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q131" t="n">
         <v>1</v>
@@ -18777,7 +18765,7 @@
         <v>0</v>
       </c>
       <c r="V131" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="W131" t="n">
         <v>0</v>
@@ -18786,16 +18774,16 @@
         <v>399</v>
       </c>
       <c r="Y131" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="Z131" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="AA131" t="n">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="AB131" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AC131" t="n">
         <v>1</v>
@@ -18813,7 +18801,7 @@
         <v>0</v>
       </c>
       <c r="AH131" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="AI131" t="n">
         <v>0</v>
@@ -18822,7 +18810,7 @@
         <v>399</v>
       </c>
       <c r="AK131" t="n">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="AL131" t="n">
         <v>370</v>
@@ -18893,13 +18881,13 @@
         <v>90</v>
       </c>
       <c r="N132" t="n">
+        <v>182</v>
+      </c>
+      <c r="O132" t="n">
         <v>188</v>
       </c>
-      <c r="O132" t="n">
-        <v>189</v>
-      </c>
       <c r="P132" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q132" t="n">
         <v>0</v>
@@ -18917,25 +18905,25 @@
         <v>0</v>
       </c>
       <c r="V132" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W132" t="n">
         <v>1</v>
       </c>
       <c r="X132" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Y132" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="Z132" t="n">
+        <v>182</v>
+      </c>
+      <c r="AA132" t="n">
         <v>188</v>
       </c>
-      <c r="AA132" t="n">
-        <v>189</v>
-      </c>
       <c r="AB132" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AC132" t="n">
         <v>0</v>
@@ -18953,16 +18941,16 @@
         <v>0</v>
       </c>
       <c r="AH132" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AI132" t="n">
         <v>1</v>
       </c>
       <c r="AJ132" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AK132" t="n">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="AL132" t="n">
         <v>368</v>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_SKALA USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_SKALA USAHA.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,237 +429,237 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH PRELIST - UB</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH PRELIST - UM</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH PRELIST - UMK</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH PRELIST - Jumlah Prelist Usaha</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - UB​</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Persentase UB​</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - UM​</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Persentase UM​</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - UMK​</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Persentase UMK​</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Total Usaha</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Persentase Total Usaha</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>

--- a/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_SKALA USAHA.xlsx
+++ b/research/fasih-dashboard-se2026/data_mikro_sls/Agregat_PCL_SKALA USAHA.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,241 +413,241 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU132"/>
+  <dimension ref="A1:AU133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Nama PCL</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Email PCL</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Nama PML</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Email PML</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>nama_kec</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>koseka</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>JUMLAH PRELIST - UB</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>JUMLAH PRELIST - UM</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>JUMLAH PRELIST - UMK</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>JUMLAH PRELIST - Jumlah Prelist Usaha</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - UB​</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Persentase UB​</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - UM​</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Persentase UM​</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - UMK​</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Persentase UMK​</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Total Usaha</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>JUMLAH DIDATA - Persentase Total Usaha</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_OPEN</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_DRAFT</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Scraped_Pencacah_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_OPEN</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_APPROVED BY Pengawas</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_DRAFT</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REJECTED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_REVOKED BY Pengawas</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_SUBMITTED RESPONDENT</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_COMPLETED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_EDITED BY Admin Kabupaten</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Total_Prelist_Scraped</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Scraped_Pengawas_Realisasi_Scraped</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>DRAFT</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>SUBMITTED BY Pencacah</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>REJECTED BY Pengawas</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>APPROVED BY Pengawas</t>
         </is>
@@ -805,19 +793,19 @@
         <v>447</v>
       </c>
       <c r="AQ2" t="n">
-        <v>364</v>
+        <v>64</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AS2" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="AT2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>4</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3">
@@ -1115,7 +1103,7 @@
         <v>342</v>
       </c>
       <c r="AQ4" t="n">
-        <v>363</v>
+        <v>94</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1127,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5">
@@ -1270,7 +1258,7 @@
         <v>249</v>
       </c>
       <c r="AQ5" t="n">
-        <v>384</v>
+        <v>184</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1279,10 +1267,10 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6">
@@ -1425,7 +1413,7 @@
         <v>233</v>
       </c>
       <c r="AQ6" t="n">
-        <v>354</v>
+        <v>166</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -1437,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7">
@@ -1580,19 +1568,19 @@
         <v>395</v>
       </c>
       <c r="AQ7" t="n">
-        <v>336</v>
+        <v>27</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8">
@@ -1735,19 +1723,19 @@
         <v>285</v>
       </c>
       <c r="AQ8" t="n">
-        <v>304</v>
+        <v>85</v>
       </c>
       <c r="AR8" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>247</v>
       </c>
     </row>
     <row r="9">
@@ -1890,19 +1878,19 @@
         <v>389</v>
       </c>
       <c r="AQ9" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10">
@@ -2045,19 +2033,19 @@
         <v>278</v>
       </c>
       <c r="AQ10" t="n">
-        <v>324</v>
+        <v>141</v>
       </c>
       <c r="AR10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -2200,19 +2188,19 @@
         <v>271</v>
       </c>
       <c r="AQ11" t="n">
-        <v>373</v>
+        <v>142</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU11" t="n">
-        <v>2</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12">
@@ -2355,19 +2343,19 @@
         <v>386</v>
       </c>
       <c r="AQ12" t="n">
-        <v>383</v>
+        <v>104</v>
       </c>
       <c r="AR12" t="n">
         <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13">
@@ -2510,19 +2498,19 @@
         <v>493</v>
       </c>
       <c r="AQ13" t="n">
-        <v>373</v>
+        <v>75</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14">
@@ -2665,19 +2653,19 @@
         <v>347</v>
       </c>
       <c r="AQ14" t="n">
-        <v>364</v>
+        <v>74</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AS14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15">
@@ -2820,19 +2808,19 @@
         <v>308</v>
       </c>
       <c r="AQ15" t="n">
-        <v>324</v>
+        <v>156</v>
       </c>
       <c r="AR15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AS15" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>263</v>
       </c>
     </row>
     <row r="16">
@@ -2975,19 +2963,19 @@
         <v>382</v>
       </c>
       <c r="AQ16" t="n">
-        <v>288</v>
+        <v>40</v>
       </c>
       <c r="AR16" t="n">
         <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17">
@@ -3061,7 +3049,7 @@
         <v>71</v>
       </c>
       <c r="T17" t="n">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="U17" t="n">
         <v>2</v>
@@ -3082,22 +3070,22 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="AD17" t="n">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="AE17" t="n">
         <v>71</v>
       </c>
       <c r="AF17" t="n">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="AG17" t="n">
         <v>2</v>
@@ -3118,31 +3106,31 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>494</v>
+        <v>529</v>
       </c>
       <c r="AP17" t="n">
-        <v>414</v>
+        <v>449</v>
       </c>
       <c r="AQ17" t="n">
-        <v>370</v>
+        <v>71</v>
       </c>
       <c r="AR17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AS17" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>410</v>
       </c>
     </row>
     <row r="18">
@@ -3285,19 +3273,19 @@
         <v>377</v>
       </c>
       <c r="AQ18" t="n">
-        <v>366</v>
+        <v>45</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AS18" t="n">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU18" t="n">
-        <v>3</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19">
@@ -3440,19 +3428,19 @@
         <v>318</v>
       </c>
       <c r="AQ19" t="n">
-        <v>423</v>
+        <v>150</v>
       </c>
       <c r="AR19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
         <v>2</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20">
@@ -3595,19 +3583,19 @@
         <v>307</v>
       </c>
       <c r="AQ20" t="n">
-        <v>284</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
     </row>
     <row r="21">
@@ -3750,19 +3738,19 @@
         <v>253</v>
       </c>
       <c r="AQ21" t="n">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="AR21" t="n">
         <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU21" t="n">
-        <v>4</v>
+        <v>213</v>
       </c>
     </row>
     <row r="22">
@@ -3797,16 +3785,16 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="J22" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
@@ -3821,31 +3809,31 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="P22" t="n">
-        <v>104.57</v>
+        <v>54.57</v>
       </c>
       <c r="Q22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R22" t="n">
-        <v>108.92</v>
+        <v>58.92</v>
       </c>
       <c r="S22" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="T22" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="U22" t="n">
         <v>1</v>
       </c>
       <c r="V22" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="W22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -3857,31 +3845,31 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="AD22" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AE22" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="AF22" t="n">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="AG22" t="n">
         <v>1</v>
       </c>
       <c r="AH22" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="AI22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AJ22" t="n">
         <v>0</v>
@@ -3893,31 +3881,31 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="AP22" t="n">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="AQ22" t="n">
-        <v>410</v>
+        <v>105</v>
       </c>
       <c r="AR22" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="AS22" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AT22" t="n">
         <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>22</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23">
@@ -4060,19 +4048,19 @@
         <v>423</v>
       </c>
       <c r="AQ23" t="n">
-        <v>450</v>
+        <v>141</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS23" t="n">
-        <v>2</v>
+        <v>59</v>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24">
@@ -4215,19 +4203,19 @@
         <v>282</v>
       </c>
       <c r="AQ24" t="n">
-        <v>359</v>
+        <v>137</v>
       </c>
       <c r="AR24" t="n">
         <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25">
@@ -4370,25 +4358,25 @@
         <v>368</v>
       </c>
       <c r="AQ25" t="n">
-        <v>308</v>
+        <v>32</v>
       </c>
       <c r="AR25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>4</v>
+        <v>297</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jessica Juanita Lombontari</t>
+          <t>NaN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4420,13 +4408,13 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -4441,31 +4429,31 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>270</v>
+        <v>50</v>
       </c>
       <c r="Q26" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>270</v>
+        <v>50</v>
       </c>
       <c r="S26" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="U26" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -4477,31 +4465,31 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="n">
-        <v>479</v>
+        <v>70</v>
       </c>
       <c r="AD26" t="n">
-        <v>309</v>
+        <v>70</v>
       </c>
       <c r="AE26" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>211</v>
+        <v>50</v>
       </c>
       <c r="AG26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
         <v>0</v>
@@ -4513,31 +4501,31 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>66</v>
+        <v>19</v>
       </c>
       <c r="AN26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO26" t="n">
-        <v>479</v>
+        <v>70</v>
       </c>
       <c r="AP26" t="n">
-        <v>307</v>
+        <v>70</v>
       </c>
       <c r="AQ26" t="n">
-        <v>419</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27">
@@ -4680,19 +4668,19 @@
         <v>387</v>
       </c>
       <c r="AQ27" t="n">
-        <v>342</v>
+        <v>56</v>
       </c>
       <c r="AR27" t="n">
         <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>3</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28">
@@ -4835,10 +4823,10 @@
         <v>375</v>
       </c>
       <c r="AQ28" t="n">
-        <v>384</v>
+        <v>109</v>
       </c>
       <c r="AR28" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="AS28" t="n">
         <v>0</v>
@@ -4847,7 +4835,7 @@
         <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
     </row>
     <row r="29">
@@ -4990,19 +4978,19 @@
         <v>343</v>
       </c>
       <c r="AQ29" t="n">
-        <v>357</v>
+        <v>133</v>
       </c>
       <c r="AR29" t="n">
         <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="30">
@@ -5145,19 +5133,19 @@
         <v>380</v>
       </c>
       <c r="AQ30" t="n">
-        <v>457</v>
+        <v>139</v>
       </c>
       <c r="AR30" t="n">
         <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31">
@@ -5300,19 +5288,19 @@
         <v>201</v>
       </c>
       <c r="AQ31" t="n">
-        <v>315</v>
+        <v>3</v>
       </c>
       <c r="AR31" t="n">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="AS31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32">
@@ -5455,19 +5443,19 @@
         <v>281</v>
       </c>
       <c r="AQ32" t="n">
-        <v>308</v>
+        <v>134</v>
       </c>
       <c r="AR32" t="n">
         <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>192</v>
       </c>
     </row>
     <row r="33">
@@ -5610,19 +5598,19 @@
         <v>282</v>
       </c>
       <c r="AQ33" t="n">
-        <v>365</v>
+        <v>156</v>
       </c>
       <c r="AR33" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AS33" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="34">
@@ -5765,19 +5753,19 @@
         <v>450</v>
       </c>
       <c r="AQ34" t="n">
-        <v>410</v>
+        <v>126</v>
       </c>
       <c r="AR34" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="AS34" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>425</v>
       </c>
     </row>
     <row r="35">
@@ -5920,19 +5908,19 @@
         <v>243</v>
       </c>
       <c r="AQ35" t="n">
-        <v>303</v>
+        <v>131</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AT35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="36">
@@ -6075,19 +6063,19 @@
         <v>477</v>
       </c>
       <c r="AQ36" t="n">
-        <v>412</v>
+        <v>93</v>
       </c>
       <c r="AR36" t="n">
         <v>0</v>
       </c>
       <c r="AS36" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>4</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37">
@@ -6230,19 +6218,19 @@
         <v>518</v>
       </c>
       <c r="AQ37" t="n">
-        <v>371</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
         <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>432</v>
       </c>
     </row>
     <row r="38">
@@ -6273,7 +6261,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6385,19 +6373,19 @@
         <v>365</v>
       </c>
       <c r="AQ38" t="n">
-        <v>453</v>
+        <v>122</v>
       </c>
       <c r="AR38" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="AS38" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>296</v>
       </c>
     </row>
     <row r="39">
@@ -6428,7 +6416,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6540,19 +6528,19 @@
         <v>313</v>
       </c>
       <c r="AQ39" t="n">
-        <v>445</v>
+        <v>152</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS39" t="n">
         <v>4</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
     </row>
     <row r="40">
@@ -6695,19 +6683,19 @@
         <v>399</v>
       </c>
       <c r="AQ40" t="n">
-        <v>379</v>
+        <v>86</v>
       </c>
       <c r="AR40" t="n">
         <v>0</v>
       </c>
       <c r="AS40" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41">
@@ -6850,19 +6838,19 @@
         <v>350</v>
       </c>
       <c r="AQ41" t="n">
-        <v>335</v>
+        <v>81</v>
       </c>
       <c r="AR41" t="n">
         <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AT41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="42">
@@ -7005,19 +6993,19 @@
         <v>387</v>
       </c>
       <c r="AQ42" t="n">
-        <v>371</v>
+        <v>127</v>
       </c>
       <c r="AR42" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="AS42" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
       <c r="AU42" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
     </row>
     <row r="43">
@@ -7160,7 +7148,7 @@
         <v>388</v>
       </c>
       <c r="AQ43" t="n">
-        <v>331</v>
+        <v>42</v>
       </c>
       <c r="AR43" t="n">
         <v>0</v>
@@ -7169,10 +7157,10 @@
         <v>13</v>
       </c>
       <c r="AT43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU43" t="n">
-        <v>1</v>
+        <v>319</v>
       </c>
     </row>
     <row r="44">
@@ -7315,7 +7303,7 @@
         <v>381</v>
       </c>
       <c r="AQ44" t="n">
-        <v>301</v>
+        <v>12</v>
       </c>
       <c r="AR44" t="n">
         <v>0</v>
@@ -7324,41 +7312,41 @@
         <v>9</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU44" t="n">
-        <v>10</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Fitrianti Tadete</t>
+          <t>Fransiska Paolin Tumbale</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>fitriantitadete68@gmail.com</t>
+          <t>fransiskapaolin@gmail.com</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Derlan Malawere</t>
+          <t>Yulianti Manambe</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>derlanmalawere92@gmail.com</t>
+          <t>anthymanambe8@gmail.com</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(092) TAHUNA BARAT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -7368,10 +7356,10 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J45" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -7386,153 +7374,153 @@
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P45" t="n">
-        <v>6.45</v>
+        <v>209.53</v>
       </c>
       <c r="Q45" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R45" t="n">
-        <v>6.45</v>
+        <v>209.53</v>
       </c>
       <c r="S45" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="T45" t="n">
-        <v>329</v>
+        <v>236</v>
       </c>
       <c r="U45" t="n">
         <v>1</v>
       </c>
       <c r="V45" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AC45" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="AD45" t="n">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="AE45" t="n">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AF45" t="n">
-        <v>329</v>
+        <v>236</v>
       </c>
       <c r="AG45" t="n">
         <v>1</v>
       </c>
       <c r="AH45" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ45" t="n">
         <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL45" t="n">
         <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AO45" t="n">
-        <v>427</v>
+        <v>477</v>
       </c>
       <c r="AP45" t="n">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="AQ45" t="n">
-        <v>355</v>
+        <v>146</v>
       </c>
       <c r="AR45" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AS45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU45" t="n">
-        <v>2</v>
+        <v>236</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Fransiska Paolin Tumbale</t>
+          <t>Frezcilia Dewi Daleda</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>fransiskapaolin@gmail.com</t>
+          <t>frzfrz130293@gmail.com</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yulianti Manambe</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>anthymanambe8@gmail.com</t>
+          <t>yanfwpadang84@gmail.com</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>(092) TAHUNA BARAT</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="J46" t="n">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>7.14</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -7541,31 +7529,31 @@
         <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="P46" t="n">
-        <v>209.53</v>
+        <v>270.72</v>
       </c>
       <c r="Q46" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="R46" t="n">
-        <v>209.53</v>
+        <v>277.87</v>
       </c>
       <c r="S46" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="T46" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="W46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
         <v>0</v>
@@ -7577,31 +7565,31 @@
         <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="AB46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>477</v>
+        <v>433</v>
       </c>
       <c r="AD46" t="n">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="AE46" t="n">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="AF46" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="AG46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="AI46" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
         <v>0</v>
@@ -7613,81 +7601,81 @@
         <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="AN46" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
-        <v>477</v>
+        <v>432</v>
       </c>
       <c r="AP46" t="n">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="AQ46" t="n">
-        <v>434</v>
+        <v>132</v>
       </c>
       <c r="AR46" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="AS46" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>241</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Frezcilia Dewi Daleda</t>
+          <t>Geovani Marchiano Monok</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>frzfrz130293@gmail.com</t>
+          <t>geovanimonok34@gmail.com</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>B. Lenskar Diamanis</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>yanfwpadang84@gmail.com</t>
+          <t>lenskardiamaniz@gmail.com</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(080) MANGANITU</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Mega</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>7.14</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -7696,153 +7684,153 @@
         <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="P47" t="n">
-        <v>270.72</v>
+        <v>65</v>
       </c>
       <c r="Q47" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="R47" t="n">
-        <v>277.87</v>
+        <v>65</v>
       </c>
       <c r="S47" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="T47" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V47" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X47" t="n">
         <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="AD47" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="AE47" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="AF47" t="n">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AH47" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ47" t="n">
         <v>0</v>
       </c>
       <c r="AK47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL47" t="n">
         <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="AN47" t="n">
         <v>0</v>
       </c>
       <c r="AO47" t="n">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="AP47" t="n">
-        <v>267</v>
+        <v>299</v>
       </c>
       <c r="AQ47" t="n">
-        <v>375</v>
+        <v>128</v>
       </c>
       <c r="AR47" t="n">
         <v>1</v>
       </c>
       <c r="AS47" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Geovani Marchiano Monok</t>
+          <t>Geno Pepa Paraso</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>geovanimonok34@gmail.com</t>
+          <t>ghenovhepaparaso@gmail.com</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B. Lenskar Diamanis</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>lenskardiamaniz@gmail.com</t>
+          <t>ferdinandtangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>(080) MANGANITU</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mega</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I48" t="n">
-        <v>27</v>
+        <v>195</v>
       </c>
       <c r="J48" t="n">
-        <v>27</v>
+        <v>209</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -7851,67 +7839,67 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
+        <v>91</v>
+      </c>
+      <c r="P48" t="n">
+        <v>132.01</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>92</v>
+      </c>
+      <c r="R48" t="n">
+        <v>132.58</v>
+      </c>
+      <c r="S48" t="n">
+        <v>121</v>
+      </c>
+      <c r="T48" t="n">
+        <v>334</v>
+      </c>
+      <c r="U48" t="n">
         <v>4</v>
       </c>
-      <c r="P48" t="n">
-        <v>65</v>
-      </c>
-      <c r="Q48" t="n">
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>485</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>364</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>121</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>334</v>
+      </c>
+      <c r="AG48" t="n">
         <v>4</v>
       </c>
-      <c r="R48" t="n">
-        <v>65</v>
-      </c>
-      <c r="S48" t="n">
-        <v>128</v>
-      </c>
-      <c r="T48" t="n">
-        <v>218</v>
-      </c>
-      <c r="U48" t="n">
-        <v>35</v>
-      </c>
-      <c r="V48" t="n">
-        <v>1</v>
-      </c>
-      <c r="W48" t="n">
-        <v>4</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>42</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>428</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>299</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>128</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>218</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>35</v>
-      </c>
       <c r="AH48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
         <v>0</v>
@@ -7923,19 +7911,19 @@
         <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO48" t="n">
-        <v>428</v>
+        <v>485</v>
       </c>
       <c r="AP48" t="n">
-        <v>299</v>
+        <v>364</v>
       </c>
       <c r="AQ48" t="n">
-        <v>363</v>
+        <v>121</v>
       </c>
       <c r="AR48" t="n">
         <v>0</v>
@@ -7944,60 +7932,60 @@
         <v>4</v>
       </c>
       <c r="AT48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="n">
-        <v>0</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Geno Pepa Paraso</t>
+          <t>Grace Dorongpangalo</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ghenovhepaparaso@gmail.com</t>
+          <t>gracedorongpangalo11@gmail.com</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Fiane Greti Mansauda</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>fianemansauda89@gmail.com</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>195</v>
+        <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>209</v>
+        <v>27</v>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.58</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
@@ -8006,134 +7994,134 @@
         <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="P49" t="n">
-        <v>132.01</v>
+        <v>333.33</v>
       </c>
       <c r="Q49" t="n">
-        <v>92</v>
+        <v>16</v>
       </c>
       <c r="R49" t="n">
-        <v>132.58</v>
+        <v>333.33</v>
       </c>
       <c r="S49" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="T49" t="n">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="U49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X49" t="n">
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AB49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC49" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="AD49" t="n">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="AE49" t="n">
-        <v>121</v>
+        <v>178</v>
       </c>
       <c r="AF49" t="n">
-        <v>334</v>
+        <v>242</v>
       </c>
       <c r="AG49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH49" t="n">
         <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ49" t="n">
         <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="AN49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO49" t="n">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="AP49" t="n">
-        <v>364</v>
+        <v>298</v>
       </c>
       <c r="AQ49" t="n">
-        <v>411</v>
+        <v>178</v>
       </c>
       <c r="AR49" t="n">
         <v>0</v>
       </c>
       <c r="AS49" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Grace Dorongpangalo</t>
+          <t>Grees Pangandaheng</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>gracedorongpangalo11@gmail.com</t>
+          <t>greispangandaheng@gmail.com</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Fiane Greti Mansauda</t>
+          <t>Novdein Arif Bongkitang</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>fianemansauda89@gmail.com</t>
+          <t>novdeinarifbongkitang@gmail.com</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(050) TAMAKO</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -8143,10 +8131,10 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="J50" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="K50" t="n">
         <v>0</v>
@@ -8161,134 +8149,134 @@
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="P50" t="n">
-        <v>333.33</v>
+        <v>375</v>
       </c>
       <c r="Q50" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="R50" t="n">
-        <v>333.33</v>
+        <v>375</v>
       </c>
       <c r="S50" t="n">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="T50" t="n">
-        <v>242</v>
+        <v>398</v>
       </c>
       <c r="U50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="X50" t="n">
         <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="AB50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="AD50" t="n">
-        <v>298</v>
+        <v>460</v>
       </c>
       <c r="AE50" t="n">
-        <v>178</v>
+        <v>61</v>
       </c>
       <c r="AF50" t="n">
-        <v>242</v>
+        <v>398</v>
       </c>
       <c r="AG50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI50" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="AJ50" t="n">
         <v>0</v>
       </c>
       <c r="AK50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="AN50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO50" t="n">
-        <v>476</v>
+        <v>539</v>
       </c>
       <c r="AP50" t="n">
-        <v>298</v>
+        <v>460</v>
       </c>
       <c r="AQ50" t="n">
-        <v>372</v>
+        <v>61</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS50" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>398</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Grees Pangandaheng</t>
+          <t>Hasrita Hamenda</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>greispangandaheng@gmail.com</t>
+          <t>hamendahasrita@gmail.com</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Novdein Arif Bongkitang</t>
+          <t>Novrilley Richard Mumu</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>novdeinarifbongkitang@gmail.com</t>
+          <t>novrilleymumu11@gmail.com</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>(050) TAMAKO</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -8298,165 +8286,165 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
+        <v>32</v>
+      </c>
+      <c r="J51" t="n">
+        <v>32</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>14</v>
+      </c>
+      <c r="P51" t="n">
+        <v>337.35</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>14</v>
+      </c>
+      <c r="R51" t="n">
+        <v>337.35</v>
+      </c>
+      <c r="S51" t="n">
+        <v>89</v>
+      </c>
+      <c r="T51" t="n">
+        <v>331</v>
+      </c>
+      <c r="U51" t="n">
         <v>8</v>
       </c>
-      <c r="J51" t="n">
+      <c r="V51" t="n">
+        <v>3</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>482</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>390</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>89</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>331</v>
+      </c>
+      <c r="AG51" t="n">
         <v>8</v>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" t="n">
-        <v>11</v>
-      </c>
-      <c r="P51" t="n">
-        <v>375</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>11</v>
-      </c>
-      <c r="R51" t="n">
-        <v>375</v>
-      </c>
-      <c r="S51" t="n">
-        <v>61</v>
-      </c>
-      <c r="T51" t="n">
-        <v>398</v>
-      </c>
-      <c r="U51" t="n">
-        <v>7</v>
-      </c>
-      <c r="V51" t="n">
-        <v>18</v>
-      </c>
-      <c r="W51" t="n">
+      <c r="AH51" t="n">
         <v>3</v>
       </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>52</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>539</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>460</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>61</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>398</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>7</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>18</v>
-      </c>
       <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>482</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>390</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>89</v>
+      </c>
+      <c r="AR51" t="n">
         <v>3</v>
       </c>
-      <c r="AJ51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>52</v>
-      </c>
-      <c r="AN51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO51" t="n">
-        <v>539</v>
-      </c>
-      <c r="AP51" t="n">
-        <v>460</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>395</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0</v>
-      </c>
       <c r="AS51" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
       <c r="AU51" t="n">
-        <v>0</v>
+        <v>331</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Hasrita Hamenda</t>
+          <t>Wahyudi Hapit</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>hamendahasrita@gmail.com</t>
+          <t>hapitudhy@gmail.com</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Novrilley Richard Mumu</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>novrilleymumu11@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="J52" t="n">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
@@ -8471,28 +8459,28 @@
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="P52" t="n">
-        <v>337.35</v>
+        <v>245.45</v>
       </c>
       <c r="Q52" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R52" t="n">
-        <v>337.35</v>
+        <v>245.45</v>
       </c>
       <c r="S52" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="T52" t="n">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="U52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="W52" t="n">
         <v>0</v>
@@ -8501,34 +8489,34 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="AB52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="AD52" t="n">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="AE52" t="n">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="AF52" t="n">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="AG52" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -8537,28 +8525,28 @@
         <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="AN52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO52" t="n">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="AP52" t="n">
-        <v>390</v>
+        <v>359</v>
       </c>
       <c r="AQ52" t="n">
-        <v>378</v>
+        <v>104</v>
       </c>
       <c r="AR52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AS52" t="n">
         <v>0</v>
@@ -8567,28 +8555,28 @@
         <v>0</v>
       </c>
       <c r="AU52" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Wahyudi Hapit</t>
+          <t>Christianto Harilama</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>hapitudhy@gmail.com</t>
+          <t>harilamachris23@gmail.com</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>vonnelariunaung77560@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -8608,10 +8596,10 @@
         <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
@@ -8626,147 +8614,147 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P53" t="n">
-        <v>345.45</v>
+        <v>500</v>
       </c>
       <c r="Q53" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R53" t="n">
-        <v>345.45</v>
+        <v>500</v>
       </c>
       <c r="S53" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="T53" t="n">
-        <v>341</v>
+        <v>219</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V53" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="X53" t="n">
         <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
       </c>
       <c r="AA53" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC53" t="n">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="AD53" t="n">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="AE53" t="n">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="AF53" t="n">
-        <v>341</v>
+        <v>219</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AH53" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AJ53" t="n">
         <v>0</v>
       </c>
       <c r="AK53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
       </c>
       <c r="AM53" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO53" t="n">
-        <v>493</v>
+        <v>452</v>
       </c>
       <c r="AP53" t="n">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="AQ53" t="n">
-        <v>429</v>
+        <v>150</v>
       </c>
       <c r="AR53" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="AS53" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AT53" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AU53" t="n">
-        <v>1</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Christianto Harilama</t>
+          <t>Sintike Susanti Meling Horman</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>harilamachris23@gmail.com</t>
+          <t>hshyntike@gmail.com</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ningsi Karendehi</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>ningsikarendehi968@gmail.com</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(061) TABUKAN SELATAN TENGAH &amp; (062) TABUKAN SELATAN TENGGARA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Erwin &amp; Lalu</t>
         </is>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="J54" t="n">
-        <v>49</v>
+        <v>8</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
@@ -8784,31 +8772,31 @@
         <v>9</v>
       </c>
       <c r="P54" t="n">
-        <v>403.57</v>
+        <v>400</v>
       </c>
       <c r="Q54" t="n">
         <v>9</v>
       </c>
       <c r="R54" t="n">
-        <v>403.57</v>
+        <v>400</v>
       </c>
       <c r="S54" t="n">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="T54" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y54" t="n">
         <v>0</v>
@@ -8817,34 +8805,34 @@
         <v>0</v>
       </c>
       <c r="AA54" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="AB54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC54" t="n">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="AD54" t="n">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="AE54" t="n">
-        <v>201</v>
+        <v>83</v>
       </c>
       <c r="AF54" t="n">
-        <v>166</v>
+        <v>235</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
       </c>
       <c r="AH54" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AI54" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK54" t="n">
         <v>0</v>
@@ -8853,81 +8841,81 @@
         <v>0</v>
       </c>
       <c r="AM54" t="n">
-        <v>12</v>
+        <v>78</v>
       </c>
       <c r="AN54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO54" t="n">
-        <v>433</v>
+        <v>400</v>
       </c>
       <c r="AP54" t="n">
-        <v>201</v>
+        <v>317</v>
       </c>
       <c r="AQ54" t="n">
-        <v>396</v>
+        <v>83</v>
       </c>
       <c r="AR54" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AS54" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AT54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU54" t="n">
-        <v>2</v>
+        <v>235</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sintike Susanti Meling Horman</t>
+          <t>Siti Nurhayati Igirisa</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>hshyntike@gmail.com</t>
+          <t>igirisatia5@gmail.com</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ningsi Karendehi</t>
+          <t>Yan Fredrik Wellian Padang</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ningsikarendehi968@gmail.com</t>
+          <t>yanfwpadang84@gmail.com</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>(061) TABUKAN SELATAN TENGAH &amp; (062) TABUKAN SELATAN TENGGARA</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Erwin &amp; Lalu</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I55" t="n">
-        <v>8</v>
+        <v>142</v>
       </c>
       <c r="J55" t="n">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -8936,34 +8924,34 @@
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="P55" t="n">
-        <v>400</v>
+        <v>373.26</v>
       </c>
       <c r="Q55" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="R55" t="n">
-        <v>400</v>
+        <v>379.14</v>
       </c>
       <c r="S55" t="n">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="T55" t="n">
-        <v>235</v>
+        <v>403</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="W55" t="n">
         <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
         <v>0</v>
@@ -8972,34 +8960,34 @@
         <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="AB55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC55" t="n">
-        <v>400</v>
+        <v>636</v>
       </c>
       <c r="AD55" t="n">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="AE55" t="n">
-        <v>83</v>
+        <v>160</v>
       </c>
       <c r="AF55" t="n">
-        <v>235</v>
+        <v>403</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
       </c>
       <c r="AJ55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK55" t="n">
         <v>0</v>
@@ -9008,81 +8996,81 @@
         <v>0</v>
       </c>
       <c r="AM55" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="AN55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO55" t="n">
-        <v>400</v>
+        <v>636</v>
       </c>
       <c r="AP55" t="n">
-        <v>317</v>
+        <v>431</v>
       </c>
       <c r="AQ55" t="n">
-        <v>279</v>
+        <v>160</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AS55" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AT55" t="n">
         <v>0</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>403</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Siti Nurhayati Igirisa</t>
+          <t>Suryaningsi Dorthea Lalompoh</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>igirisatia5@gmail.com</t>
+          <t>indrydorthea@gmail.com</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Yan Fredrik Wellian Padang</t>
+          <t>Jekir Venkil Dompas</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>yanfwpadang84@gmail.com</t>
+          <t>jekirvenkildompas@gmail.com</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Kharis</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>142</v>
+        <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>150</v>
+        <v>29</v>
       </c>
       <c r="K56" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0</v>
@@ -9091,31 +9079,31 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="P56" t="n">
-        <v>373.26</v>
+        <v>367.86</v>
       </c>
       <c r="Q56" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="R56" t="n">
-        <v>379.14</v>
+        <v>367.86</v>
       </c>
       <c r="S56" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="T56" t="n">
-        <v>403</v>
+        <v>215</v>
       </c>
       <c r="U56" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="V56" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X56" t="n">
         <v>0</v>
@@ -9127,31 +9115,31 @@
         <v>0</v>
       </c>
       <c r="AA56" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="AB56" t="n">
         <v>1</v>
       </c>
       <c r="AC56" t="n">
-        <v>636</v>
+        <v>493</v>
       </c>
       <c r="AD56" t="n">
-        <v>431</v>
+        <v>328</v>
       </c>
       <c r="AE56" t="n">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="AF56" t="n">
-        <v>403</v>
+        <v>215</v>
       </c>
       <c r="AG56" t="n">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="AH56" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ56" t="n">
         <v>0</v>
@@ -9163,62 +9151,62 @@
         <v>0</v>
       </c>
       <c r="AM56" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="AN56" t="n">
         <v>1</v>
       </c>
       <c r="AO56" t="n">
-        <v>636</v>
+        <v>493</v>
       </c>
       <c r="AP56" t="n">
-        <v>431</v>
+        <v>328</v>
       </c>
       <c r="AQ56" t="n">
-        <v>420</v>
+        <v>148</v>
       </c>
       <c r="AR56" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS56" t="n">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="AT56" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU56" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Suryaningsi Dorthea Lalompoh</t>
+          <t>Asiantina Maniku</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>indrydorthea@gmail.com</t>
+          <t>iyanmaniku1@gmail.com</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jekir Venkil Dompas</t>
+          <t>Derlan Malawere</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>jekirvenkildompas@gmail.com</t>
+          <t>derlanmalawere92@gmail.com</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>(070) TABUKAN TENGAH</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kharis</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -9228,10 +9216,10 @@
         <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J57" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -9246,31 +9234,31 @@
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="P57" t="n">
-        <v>367.86</v>
+        <v>6.45</v>
       </c>
       <c r="Q57" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="R57" t="n">
-        <v>367.86</v>
+        <v>6.45</v>
       </c>
       <c r="S57" t="n">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="T57" t="n">
-        <v>215</v>
+        <v>329</v>
       </c>
       <c r="U57" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="V57" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="W57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X57" t="n">
         <v>0</v>
@@ -9282,31 +9270,31 @@
         <v>0</v>
       </c>
       <c r="AA57" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AB57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC57" t="n">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="AD57" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AE57" t="n">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="AF57" t="n">
-        <v>215</v>
+        <v>329</v>
       </c>
       <c r="AG57" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="AH57" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AI57" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AJ57" t="n">
         <v>0</v>
@@ -9318,31 +9306,31 @@
         <v>0</v>
       </c>
       <c r="AM57" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="AN57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO57" t="n">
-        <v>493</v>
+        <v>427</v>
       </c>
       <c r="AP57" t="n">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AQ57" t="n">
-        <v>336</v>
+        <v>85</v>
       </c>
       <c r="AR57" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AS57" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AT57" t="n">
         <v>0</v>
       </c>
       <c r="AU57" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="58">
@@ -9485,19 +9473,19 @@
         <v>267</v>
       </c>
       <c r="AQ58" t="n">
-        <v>363</v>
+        <v>194</v>
       </c>
       <c r="AR58" t="n">
         <v>0</v>
       </c>
       <c r="AS58" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AT58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU58" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="59">
@@ -9640,19 +9628,19 @@
         <v>364</v>
       </c>
       <c r="AQ59" t="n">
-        <v>383</v>
+        <v>108</v>
       </c>
       <c r="AR59" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AS59" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AT59" t="n">
         <v>0</v>
       </c>
       <c r="AU59" t="n">
-        <v>1</v>
+        <v>252</v>
       </c>
     </row>
     <row r="60">
@@ -9795,19 +9783,19 @@
         <v>289</v>
       </c>
       <c r="AQ60" t="n">
-        <v>377</v>
+        <v>160</v>
       </c>
       <c r="AR60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS60" t="n">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AU60" t="n">
-        <v>0</v>
+        <v>142</v>
       </c>
     </row>
     <row r="61">
@@ -9950,19 +9938,19 @@
         <v>238</v>
       </c>
       <c r="AQ61" t="n">
-        <v>314</v>
+        <v>126</v>
       </c>
       <c r="AR61" t="n">
         <v>0</v>
       </c>
       <c r="AS61" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AT61" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU61" t="n">
-        <v>0</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62">
@@ -10105,19 +10093,19 @@
         <v>440</v>
       </c>
       <c r="AQ62" t="n">
-        <v>365</v>
+        <v>79</v>
       </c>
       <c r="AR62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS62" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="AT62" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AU62" t="n">
-        <v>6</v>
+        <v>345</v>
       </c>
     </row>
     <row r="63">
@@ -10260,19 +10248,19 @@
         <v>373</v>
       </c>
       <c r="AQ63" t="n">
-        <v>324</v>
+        <v>99</v>
       </c>
       <c r="AR63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS63" t="n">
         <v>0</v>
       </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU63" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64">
@@ -10415,19 +10403,19 @@
         <v>394</v>
       </c>
       <c r="AQ64" t="n">
-        <v>440</v>
+        <v>157</v>
       </c>
       <c r="AR64" t="n">
         <v>0</v>
       </c>
       <c r="AS64" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AT64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU64" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
     </row>
     <row r="65">
@@ -10570,19 +10558,19 @@
         <v>357</v>
       </c>
       <c r="AQ65" t="n">
-        <v>417</v>
+        <v>105</v>
       </c>
       <c r="AR65" t="n">
         <v>0</v>
       </c>
       <c r="AS65" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AT65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU65" t="n">
-        <v>0</v>
+        <v>291</v>
       </c>
     </row>
     <row r="66">
@@ -10725,19 +10713,19 @@
         <v>397</v>
       </c>
       <c r="AQ66" t="n">
-        <v>384</v>
+        <v>78</v>
       </c>
       <c r="AR66" t="n">
         <v>0</v>
       </c>
       <c r="AS66" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU66" t="n">
-        <v>2</v>
+        <v>316</v>
       </c>
     </row>
     <row r="67">
@@ -10880,19 +10868,19 @@
         <v>255</v>
       </c>
       <c r="AQ67" t="n">
-        <v>297</v>
+        <v>100</v>
       </c>
       <c r="AR67" t="n">
         <v>0</v>
       </c>
       <c r="AS67" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AT67" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AU67" t="n">
-        <v>1</v>
+        <v>185</v>
       </c>
     </row>
     <row r="68">
@@ -11035,19 +11023,19 @@
         <v>504</v>
       </c>
       <c r="AQ68" t="n">
-        <v>395</v>
+        <v>21</v>
       </c>
       <c r="AR68" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS68" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AT68" t="n">
         <v>1</v>
       </c>
       <c r="AU68" t="n">
-        <v>8</v>
+        <v>448</v>
       </c>
     </row>
     <row r="69">
@@ -11190,19 +11178,19 @@
         <v>300</v>
       </c>
       <c r="AQ69" t="n">
-        <v>317</v>
+        <v>101</v>
       </c>
       <c r="AR69" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS69" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="AT69" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AU69" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
     </row>
     <row r="70">
@@ -11345,19 +11333,19 @@
         <v>224</v>
       </c>
       <c r="AQ70" t="n">
-        <v>306</v>
+        <v>131</v>
       </c>
       <c r="AR70" t="n">
         <v>0</v>
       </c>
       <c r="AS70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
       <c r="AU70" t="n">
-        <v>0</v>
+        <v>195</v>
       </c>
     </row>
     <row r="71">
@@ -11500,19 +11488,19 @@
         <v>441</v>
       </c>
       <c r="AQ71" t="n">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="AR71" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AS71" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AT71" t="n">
         <v>0</v>
       </c>
       <c r="AU71" t="n">
-        <v>0</v>
+        <v>391</v>
       </c>
     </row>
     <row r="72">
@@ -11655,19 +11643,19 @@
         <v>578</v>
       </c>
       <c r="AQ72" t="n">
-        <v>353</v>
+        <v>3</v>
       </c>
       <c r="AR72" t="n">
         <v>0</v>
       </c>
       <c r="AS72" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AT72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU72" t="n">
-        <v>0</v>
+        <v>492</v>
       </c>
     </row>
     <row r="73">
@@ -11810,19 +11798,19 @@
         <v>331</v>
       </c>
       <c r="AQ73" t="n">
-        <v>362</v>
+        <v>105</v>
       </c>
       <c r="AR73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS73" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AT73" t="n">
         <v>0</v>
       </c>
       <c r="AU73" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
     </row>
     <row r="74">
@@ -11965,10 +11953,10 @@
         <v>472</v>
       </c>
       <c r="AQ74" t="n">
-        <v>398</v>
+        <v>19</v>
       </c>
       <c r="AR74" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="AS74" t="n">
         <v>0</v>
@@ -11977,7 +11965,7 @@
         <v>0</v>
       </c>
       <c r="AU74" t="n">
-        <v>0</v>
+        <v>386</v>
       </c>
     </row>
     <row r="75">
@@ -12120,19 +12108,19 @@
         <v>283</v>
       </c>
       <c r="AQ75" t="n">
-        <v>359</v>
+        <v>138</v>
       </c>
       <c r="AR75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AS75" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AT75" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AU75" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="76">
@@ -12275,19 +12263,19 @@
         <v>251</v>
       </c>
       <c r="AQ76" t="n">
-        <v>357</v>
+        <v>175</v>
       </c>
       <c r="AR76" t="n">
         <v>0</v>
       </c>
       <c r="AS76" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU76" t="n">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="77">
@@ -12430,19 +12418,19 @@
         <v>430</v>
       </c>
       <c r="AQ77" t="n">
-        <v>386</v>
+        <v>87</v>
       </c>
       <c r="AR77" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="AS77" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="AT77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU77" t="n">
-        <v>7</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78">
@@ -12585,19 +12573,19 @@
         <v>306</v>
       </c>
       <c r="AQ78" t="n">
-        <v>350</v>
+        <v>114</v>
       </c>
       <c r="AR78" t="n">
         <v>0</v>
       </c>
       <c r="AS78" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU78" t="n">
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79">
@@ -12740,7 +12728,7 @@
         <v>394</v>
       </c>
       <c r="AQ79" t="n">
-        <v>319</v>
+        <v>21</v>
       </c>
       <c r="AR79" t="n">
         <v>0</v>
@@ -12749,54 +12737,54 @@
         <v>6</v>
       </c>
       <c r="AT79" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU79" t="n">
-        <v>7</v>
+        <v>313</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Mery Grace Anabelia Kantohe</t>
+          <t>Aldo Jhon Mesak Bangonang</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>merykantohe979@gmail.com</t>
+          <t>mesakbangonang99@gmail.com</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="J80" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="K80" t="n">
         <v>0</v>
@@ -12811,103 +12799,103 @@
         <v>0</v>
       </c>
       <c r="O80" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="P80" t="n">
-        <v>145</v>
+        <v>123.57</v>
       </c>
       <c r="Q80" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="R80" t="n">
-        <v>145</v>
+        <v>123.57</v>
       </c>
       <c r="S80" t="n">
-        <v>95</v>
+        <v>211</v>
       </c>
       <c r="T80" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="U80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V80" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W80" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="X80" t="n">
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z80" t="n">
         <v>0</v>
       </c>
       <c r="AA80" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AB80" t="n">
         <v>0</v>
       </c>
       <c r="AC80" t="n">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="AD80" t="n">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="AE80" t="n">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="AF80" t="n">
-        <v>149</v>
+        <v>108</v>
       </c>
       <c r="AG80" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AH80" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AI80" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="AJ80" t="n">
         <v>0</v>
       </c>
       <c r="AK80" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL80" t="n">
         <v>0</v>
       </c>
       <c r="AM80" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AN80" t="n">
         <v>0</v>
       </c>
       <c r="AO80" t="n">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="AP80" t="n">
-        <v>194</v>
+        <v>159</v>
       </c>
       <c r="AQ80" t="n">
-        <v>263</v>
+        <v>211</v>
       </c>
       <c r="AR80" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="AS80" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AT80" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU80" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
     </row>
     <row r="81">
@@ -13050,19 +13038,19 @@
         <v>292</v>
       </c>
       <c r="AQ81" t="n">
-        <v>313</v>
+        <v>60</v>
       </c>
       <c r="AR81" t="n">
         <v>0</v>
       </c>
       <c r="AS81" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AT81" t="n">
         <v>0</v>
       </c>
       <c r="AU81" t="n">
-        <v>0</v>
+        <v>262</v>
       </c>
     </row>
     <row r="82">
@@ -13205,19 +13193,19 @@
         <v>330</v>
       </c>
       <c r="AQ82" t="n">
-        <v>385</v>
+        <v>113</v>
       </c>
       <c r="AR82" t="n">
         <v>0</v>
       </c>
       <c r="AS82" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AT82" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU82" t="n">
-        <v>0</v>
+        <v>282</v>
       </c>
     </row>
     <row r="83">
@@ -13360,19 +13348,19 @@
         <v>299</v>
       </c>
       <c r="AQ83" t="n">
-        <v>340</v>
+        <v>159</v>
       </c>
       <c r="AR83" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AS83" t="n">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AU83" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
     </row>
     <row r="84">
@@ -13515,19 +13503,19 @@
         <v>316</v>
       </c>
       <c r="AQ84" t="n">
-        <v>378</v>
+        <v>111</v>
       </c>
       <c r="AR84" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="AS84" t="n">
         <v>0</v>
       </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU84" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85">
@@ -13670,19 +13658,19 @@
         <v>299</v>
       </c>
       <c r="AQ85" t="n">
-        <v>367</v>
+        <v>126</v>
       </c>
       <c r="AR85" t="n">
         <v>0</v>
       </c>
       <c r="AS85" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT85" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU85" t="n">
-        <v>0</v>
+        <v>236</v>
       </c>
     </row>
     <row r="86">
@@ -13825,19 +13813,19 @@
         <v>327</v>
       </c>
       <c r="AQ86" t="n">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="AR86" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AS86" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AT86" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AU86" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
     </row>
     <row r="87">
@@ -13980,19 +13968,19 @@
         <v>278</v>
       </c>
       <c r="AQ87" t="n">
-        <v>360</v>
+        <v>146</v>
       </c>
       <c r="AR87" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="AS87" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AT87" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU87" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
     </row>
     <row r="88">
@@ -14135,19 +14123,19 @@
         <v>362</v>
       </c>
       <c r="AQ88" t="n">
-        <v>356</v>
+        <v>70</v>
       </c>
       <c r="AR88" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="AS88" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU88" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
     </row>
     <row r="89">
@@ -14290,19 +14278,19 @@
         <v>333</v>
       </c>
       <c r="AQ89" t="n">
-        <v>405</v>
+        <v>167</v>
       </c>
       <c r="AR89" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AS89" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="n">
         <v>2</v>
       </c>
-      <c r="AT89" t="n">
-        <v>0</v>
-      </c>
       <c r="AU89" t="n">
-        <v>0</v>
+        <v>264</v>
       </c>
     </row>
     <row r="90">
@@ -14445,19 +14433,19 @@
         <v>239</v>
       </c>
       <c r="AQ90" t="n">
-        <v>301</v>
+        <v>51</v>
       </c>
       <c r="AR90" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AS90" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="AT90" t="n">
         <v>0</v>
       </c>
       <c r="AU90" t="n">
-        <v>0</v>
+        <v>207</v>
       </c>
     </row>
     <row r="91">
@@ -14600,19 +14588,19 @@
         <v>316</v>
       </c>
       <c r="AQ91" t="n">
-        <v>399</v>
+        <v>127</v>
       </c>
       <c r="AR91" t="n">
         <v>0</v>
       </c>
       <c r="AS91" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AT91" t="n">
         <v>0</v>
       </c>
       <c r="AU91" t="n">
-        <v>0</v>
+        <v>293</v>
       </c>
     </row>
     <row r="92">
@@ -14755,19 +14743,19 @@
         <v>360</v>
       </c>
       <c r="AQ92" t="n">
-        <v>364</v>
+        <v>108</v>
       </c>
       <c r="AR92" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS92" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AT92" t="n">
         <v>0</v>
       </c>
       <c r="AU92" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
     </row>
     <row r="93">
@@ -14910,19 +14898,19 @@
         <v>381</v>
       </c>
       <c r="AQ93" t="n">
-        <v>335</v>
+        <v>42</v>
       </c>
       <c r="AR93" t="n">
         <v>0</v>
       </c>
       <c r="AS93" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AT93" t="n">
         <v>0</v>
       </c>
       <c r="AU93" t="n">
-        <v>0</v>
+        <v>347</v>
       </c>
     </row>
     <row r="94">
@@ -15065,10 +15053,10 @@
         <v>278</v>
       </c>
       <c r="AQ94" t="n">
-        <v>373</v>
+        <v>164</v>
       </c>
       <c r="AR94" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="AS94" t="n">
         <v>4</v>
@@ -15077,7 +15065,7 @@
         <v>0</v>
       </c>
       <c r="AU94" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
     </row>
     <row r="95">
@@ -15220,19 +15208,19 @@
         <v>382</v>
       </c>
       <c r="AQ95" t="n">
-        <v>356</v>
+        <v>47</v>
       </c>
       <c r="AR95" t="n">
         <v>0</v>
       </c>
       <c r="AS95" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AT95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU95" t="n">
-        <v>3</v>
+        <v>325</v>
       </c>
     </row>
     <row r="96">
@@ -15375,19 +15363,19 @@
         <v>366</v>
       </c>
       <c r="AQ96" t="n">
-        <v>282</v>
+        <v>30</v>
       </c>
       <c r="AR96" t="n">
         <v>0</v>
       </c>
       <c r="AS96" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="AT96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU96" t="n">
-        <v>1</v>
+        <v>247</v>
       </c>
     </row>
     <row r="97">
@@ -15530,19 +15518,19 @@
         <v>360</v>
       </c>
       <c r="AQ97" t="n">
-        <v>378</v>
+        <v>21</v>
       </c>
       <c r="AR97" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="AS97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT97" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AU97" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="98">
@@ -15685,19 +15673,19 @@
         <v>248</v>
       </c>
       <c r="AQ98" t="n">
-        <v>367</v>
+        <v>152</v>
       </c>
       <c r="AR98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS98" t="n">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="AT98" t="n">
         <v>0</v>
       </c>
       <c r="AU98" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
     </row>
     <row r="99">
@@ -15840,19 +15828,19 @@
         <v>347</v>
       </c>
       <c r="AQ99" t="n">
-        <v>321</v>
+        <v>87</v>
       </c>
       <c r="AR99" t="n">
         <v>0</v>
       </c>
       <c r="AS99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU99" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
     </row>
     <row r="100">
@@ -15995,19 +15983,19 @@
         <v>277</v>
       </c>
       <c r="AQ100" t="n">
-        <v>343</v>
+        <v>161</v>
       </c>
       <c r="AR100" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS100" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="n">
-        <v>0</v>
+        <v>210</v>
       </c>
     </row>
     <row r="101">
@@ -16150,19 +16138,19 @@
         <v>399</v>
       </c>
       <c r="AQ101" t="n">
-        <v>455</v>
+        <v>134</v>
       </c>
       <c r="AR101" t="n">
         <v>0</v>
       </c>
       <c r="AS101" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AT101" t="n">
         <v>0</v>
       </c>
       <c r="AU101" t="n">
-        <v>0</v>
+        <v>281</v>
       </c>
     </row>
     <row r="102">
@@ -16193,7 +16181,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -16305,19 +16293,19 @@
         <v>318</v>
       </c>
       <c r="AQ102" t="n">
-        <v>472</v>
+        <v>192</v>
       </c>
       <c r="AR102" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS102" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT102" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU102" t="n">
-        <v>0</v>
+        <v>248</v>
       </c>
     </row>
     <row r="103">
@@ -16460,19 +16448,19 @@
         <v>427</v>
       </c>
       <c r="AQ103" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="AR103" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AS103" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="AT103" t="n">
         <v>0</v>
       </c>
       <c r="AU103" t="n">
-        <v>0</v>
+        <v>364</v>
       </c>
     </row>
     <row r="104">
@@ -16503,7 +16491,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Suharsi</t>
+          <t>Begin</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -16615,19 +16603,19 @@
         <v>296</v>
       </c>
       <c r="AQ104" t="n">
-        <v>422</v>
+        <v>139</v>
       </c>
       <c r="AR104" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AS104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AT104" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU104" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
     </row>
     <row r="105">
@@ -16668,10 +16656,10 @@
         <v>0</v>
       </c>
       <c r="I105" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J105" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K105" t="n">
         <v>0</v>
@@ -16686,22 +16674,22 @@
         <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P105" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="Q105" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R105" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="S105" t="n">
         <v>87</v>
       </c>
       <c r="T105" t="n">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="U105" t="n">
         <v>16</v>
@@ -16722,22 +16710,22 @@
         <v>0</v>
       </c>
       <c r="AA105" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="AB105" t="n">
         <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="AD105" t="n">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="AE105" t="n">
         <v>87</v>
       </c>
       <c r="AF105" t="n">
-        <v>304</v>
+        <v>350</v>
       </c>
       <c r="AG105" t="n">
         <v>16</v>
@@ -16758,31 +16746,31 @@
         <v>0</v>
       </c>
       <c r="AM105" t="n">
-        <v>86</v>
+        <v>63</v>
       </c>
       <c r="AN105" t="n">
         <v>0</v>
       </c>
       <c r="AO105" t="n">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="AP105" t="n">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="AQ105" t="n">
-        <v>391</v>
+        <v>87</v>
       </c>
       <c r="AR105" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AS105" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AT105" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="n">
-        <v>5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="106">
@@ -16925,19 +16913,19 @@
         <v>395</v>
       </c>
       <c r="AQ106" t="n">
-        <v>366</v>
+        <v>113</v>
       </c>
       <c r="AR106" t="n">
         <v>1</v>
       </c>
       <c r="AS106" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="AT106" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AU106" t="n">
-        <v>11</v>
+        <v>299</v>
       </c>
     </row>
     <row r="107">
@@ -17080,19 +17068,19 @@
         <v>307</v>
       </c>
       <c r="AQ107" t="n">
-        <v>322</v>
+        <v>72</v>
       </c>
       <c r="AR107" t="n">
         <v>0</v>
       </c>
       <c r="AS107" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AT107" t="n">
         <v>0</v>
       </c>
       <c r="AU107" t="n">
-        <v>0</v>
+        <v>231</v>
       </c>
     </row>
     <row r="108">
@@ -17235,19 +17223,19 @@
         <v>368</v>
       </c>
       <c r="AQ108" t="n">
-        <v>324</v>
+        <v>32</v>
       </c>
       <c r="AR108" t="n">
         <v>0</v>
       </c>
       <c r="AS108" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AT108" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AU108" t="n">
-        <v>5</v>
+        <v>304</v>
       </c>
     </row>
     <row r="109">
@@ -17390,10 +17378,10 @@
         <v>313</v>
       </c>
       <c r="AQ109" t="n">
-        <v>407</v>
+        <v>193</v>
       </c>
       <c r="AR109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS109" t="n">
         <v>2</v>
@@ -17402,7 +17390,7 @@
         <v>0</v>
       </c>
       <c r="AU109" t="n">
-        <v>0</v>
+        <v>269</v>
       </c>
     </row>
     <row r="110">
@@ -17545,10 +17533,10 @@
         <v>404</v>
       </c>
       <c r="AQ110" t="n">
-        <v>507</v>
+        <v>213</v>
       </c>
       <c r="AR110" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AS110" t="n">
         <v>0</v>
@@ -17557,7 +17545,7 @@
         <v>3</v>
       </c>
       <c r="AU110" t="n">
-        <v>2</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111">
@@ -17700,19 +17688,19 @@
         <v>307</v>
       </c>
       <c r="AQ111" t="n">
-        <v>294</v>
+        <v>109</v>
       </c>
       <c r="AR111" t="n">
         <v>0</v>
       </c>
       <c r="AS111" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AT111" t="n">
         <v>0</v>
       </c>
       <c r="AU111" t="n">
-        <v>0</v>
+        <v>255</v>
       </c>
     </row>
     <row r="112">
@@ -17855,19 +17843,19 @@
         <v>262</v>
       </c>
       <c r="AQ112" t="n">
-        <v>403</v>
+        <v>178</v>
       </c>
       <c r="AR112" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AS112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="n">
-        <v>0</v>
+        <v>243</v>
       </c>
     </row>
     <row r="113">
@@ -18010,19 +17998,19 @@
         <v>442</v>
       </c>
       <c r="AQ113" t="n">
-        <v>362</v>
+        <v>87</v>
       </c>
       <c r="AR113" t="n">
         <v>0</v>
       </c>
       <c r="AS113" t="n">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="AT113" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AU113" t="n">
-        <v>2</v>
+        <v>286</v>
       </c>
     </row>
     <row r="114">
@@ -18165,19 +18153,19 @@
         <v>561</v>
       </c>
       <c r="AQ114" t="n">
-        <v>382</v>
+        <v>0</v>
       </c>
       <c r="AR114" t="n">
         <v>0</v>
       </c>
       <c r="AS114" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AT114" t="n">
         <v>0</v>
       </c>
       <c r="AU114" t="n">
-        <v>0</v>
+        <v>445</v>
       </c>
     </row>
     <row r="115">
@@ -18320,19 +18308,19 @@
         <v>271</v>
       </c>
       <c r="AQ115" t="n">
-        <v>344</v>
+        <v>162</v>
       </c>
       <c r="AR115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS115" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT115" t="n">
         <v>0</v>
       </c>
       <c r="AU115" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
     </row>
     <row r="116">
@@ -18475,50 +18463,50 @@
         <v>292</v>
       </c>
       <c r="AQ116" t="n">
-        <v>333</v>
+        <v>102</v>
       </c>
       <c r="AR116" t="n">
         <v>0</v>
       </c>
       <c r="AS116" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="AT116" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU116" t="n">
-        <v>0</v>
+        <v>224</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Stevanus Francois Mangeghong</t>
+          <t>Srirahayu Durumias</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>stivfrancois@gmail.com</t>
+          <t>srirahayudurumias@gmail.com</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Fresly Jeica Manangkoda</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>fmanangkoda12@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>(050) TAMAKO</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Erike</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -18528,10 +18516,10 @@
         <v>0</v>
       </c>
       <c r="I117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J117" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K117" t="n">
         <v>0</v>
@@ -18546,37 +18534,37 @@
         <v>0</v>
       </c>
       <c r="O117" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P117" t="n">
-        <v>533.34</v>
+        <v>145</v>
       </c>
       <c r="Q117" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="R117" t="n">
-        <v>533.34</v>
+        <v>145</v>
       </c>
       <c r="S117" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="T117" t="n">
-        <v>320</v>
+        <v>149</v>
       </c>
       <c r="U117" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V117" t="n">
         <v>0</v>
       </c>
       <c r="W117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X117" t="n">
         <v>0</v>
       </c>
       <c r="Y117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z117" t="n">
         <v>0</v>
@@ -18588,31 +18576,31 @@
         <v>0</v>
       </c>
       <c r="AC117" t="n">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="AD117" t="n">
-        <v>371</v>
+        <v>194</v>
       </c>
       <c r="AE117" t="n">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="AF117" t="n">
-        <v>320</v>
+        <v>149</v>
       </c>
       <c r="AG117" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AH117" t="n">
         <v>0</v>
       </c>
       <c r="AI117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ117" t="n">
         <v>0</v>
       </c>
       <c r="AK117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL117" t="n">
         <v>0</v>
@@ -18624,69 +18612,69 @@
         <v>0</v>
       </c>
       <c r="AO117" t="n">
-        <v>435</v>
+        <v>289</v>
       </c>
       <c r="AP117" t="n">
-        <v>371</v>
+        <v>194</v>
       </c>
       <c r="AQ117" t="n">
-        <v>364</v>
+        <v>95</v>
       </c>
       <c r="AR117" t="n">
         <v>0</v>
       </c>
       <c r="AS117" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AT117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU117" t="n">
-        <v>6</v>
+        <v>149</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sulastri Bawenti</t>
+          <t>Stevanus Francois Mangeghong</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>sulastribwnti@gmail.com</t>
+          <t>stivfrancois@gmail.com</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sutrisno Sariang</t>
+          <t>Fresly Jeica Manangkoda</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>sutrisnosariang90@gmail.com</t>
+          <t>fmanangkoda12@gmail.com</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>(100) TABUKAN UTARA</t>
+          <t>(050) TAMAKO</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Hendri</t>
+          <t>Erike</t>
         </is>
       </c>
       <c r="G118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
       </c>
       <c r="I118" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J118" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K118" t="n">
         <v>0</v>
@@ -18704,22 +18692,22 @@
         <v>10</v>
       </c>
       <c r="P118" t="n">
-        <v>294.44</v>
+        <v>533.34</v>
       </c>
       <c r="Q118" t="n">
         <v>10</v>
       </c>
       <c r="R118" t="n">
-        <v>294.44</v>
+        <v>533.34</v>
       </c>
       <c r="S118" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="T118" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="U118" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V118" t="n">
         <v>0</v>
@@ -18740,22 +18728,22 @@
         <v>42</v>
       </c>
       <c r="AB118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC118" t="n">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="AD118" t="n">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="AE118" t="n">
-        <v>134</v>
+        <v>64</v>
       </c>
       <c r="AF118" t="n">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="AG118" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AH118" t="n">
         <v>0</v>
@@ -18776,72 +18764,72 @@
         <v>42</v>
       </c>
       <c r="AN118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO118" t="n">
-        <v>537</v>
+        <v>435</v>
       </c>
       <c r="AP118" t="n">
-        <v>403</v>
+        <v>371</v>
       </c>
       <c r="AQ118" t="n">
-        <v>378</v>
+        <v>64</v>
       </c>
       <c r="AR118" t="n">
         <v>0</v>
       </c>
       <c r="AS118" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT118" t="n">
         <v>0</v>
       </c>
       <c r="AU118" t="n">
-        <v>0</v>
+        <v>320</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sunardi Tamado</t>
+          <t>Sulastri Bawenti</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>sunarditamado2@gmail.com</t>
+          <t>sulastribwnti@gmail.com</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Sutrisno Sariang</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>sutrisnosariang90@gmail.com</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(100) TABUKAN UTARA</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Hendri</t>
         </is>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
       </c>
       <c r="I119" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="J119" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="K119" t="n">
         <v>0</v>
@@ -18856,25 +18844,25 @@
         <v>0</v>
       </c>
       <c r="O119" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P119" t="n">
-        <v>56.41</v>
+        <v>294.44</v>
       </c>
       <c r="Q119" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R119" t="n">
-        <v>56.41</v>
+        <v>294.44</v>
       </c>
       <c r="S119" t="n">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="T119" t="n">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="U119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V119" t="n">
         <v>0</v>
@@ -18886,31 +18874,31 @@
         <v>0</v>
       </c>
       <c r="Y119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z119" t="n">
         <v>0</v>
       </c>
       <c r="AA119" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="AB119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AC119" t="n">
-        <v>486</v>
+        <v>537</v>
       </c>
       <c r="AD119" t="n">
-        <v>442</v>
+        <v>403</v>
       </c>
       <c r="AE119" t="n">
-        <v>44</v>
+        <v>134</v>
       </c>
       <c r="AF119" t="n">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="AG119" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH119" t="n">
         <v>0</v>
@@ -18922,68 +18910,68 @@
         <v>0</v>
       </c>
       <c r="AK119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL119" t="n">
         <v>0</v>
       </c>
       <c r="AM119" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="AN119" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO119" t="n">
-        <v>486</v>
+        <v>537</v>
       </c>
       <c r="AP119" t="n">
-        <v>442</v>
+        <v>403</v>
       </c>
       <c r="AQ119" t="n">
-        <v>420</v>
+        <v>134</v>
       </c>
       <c r="AR119" t="n">
         <v>0</v>
       </c>
       <c r="AS119" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AT119" t="n">
         <v>0</v>
       </c>
       <c r="AU119" t="n">
-        <v>0</v>
+        <v>360</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Oktavianti Tangkabiringan</t>
+          <t>Sunardi Tamado</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>tangkabiringananti@gmail.com</t>
+          <t>sunarditamado2@gmail.com</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -18993,10 +18981,10 @@
         <v>0</v>
       </c>
       <c r="I120" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="J120" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -19011,25 +18999,25 @@
         <v>0</v>
       </c>
       <c r="O120" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="P120" t="n">
-        <v>416.67</v>
+        <v>56.41</v>
       </c>
       <c r="Q120" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="R120" t="n">
-        <v>416.67</v>
+        <v>56.41</v>
       </c>
       <c r="S120" t="n">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="T120" t="n">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="U120" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="V120" t="n">
         <v>0</v>
@@ -19041,31 +19029,31 @@
         <v>0</v>
       </c>
       <c r="Y120" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>58</v>
+      </c>
+      <c r="AB120" t="n">
         <v>3</v>
       </c>
-      <c r="Z120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA120" t="n">
-        <v>96</v>
-      </c>
-      <c r="AB120" t="n">
-        <v>0</v>
-      </c>
       <c r="AC120" t="n">
-        <v>544</v>
+        <v>486</v>
       </c>
       <c r="AD120" t="n">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="AE120" t="n">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="AF120" t="n">
-        <v>266</v>
+        <v>378</v>
       </c>
       <c r="AG120" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AH120" t="n">
         <v>0</v>
@@ -19077,68 +19065,68 @@
         <v>0</v>
       </c>
       <c r="AK120" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>58</v>
+      </c>
+      <c r="AN120" t="n">
         <v>3</v>
       </c>
-      <c r="AL120" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM120" t="n">
-        <v>96</v>
-      </c>
-      <c r="AN120" t="n">
-        <v>0</v>
-      </c>
       <c r="AO120" t="n">
-        <v>544</v>
+        <v>486</v>
       </c>
       <c r="AP120" t="n">
-        <v>380</v>
+        <v>442</v>
       </c>
       <c r="AQ120" t="n">
-        <v>430</v>
+        <v>44</v>
       </c>
       <c r="AR120" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AS120" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT120" t="n">
         <v>0</v>
       </c>
       <c r="AU120" t="n">
-        <v>0</v>
+        <v>378</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Ambrosius Tampi Tangkabiringan</t>
+          <t>Oktavianti Tangkabiringan</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>tangkabiringanayen70@gmail.com</t>
+          <t>tangkabiringananti@gmail.com</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>georgemulersasiangsasiang@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -19148,10 +19136,10 @@
         <v>0</v>
       </c>
       <c r="I121" t="n">
-        <v>178</v>
+        <v>23</v>
       </c>
       <c r="J121" t="n">
-        <v>178</v>
+        <v>23</v>
       </c>
       <c r="K121" t="n">
         <v>0</v>
@@ -19166,28 +19154,28 @@
         <v>0</v>
       </c>
       <c r="O121" t="n">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="P121" t="n">
-        <v>214.85</v>
+        <v>416.67</v>
       </c>
       <c r="Q121" t="n">
-        <v>118</v>
+        <v>17</v>
       </c>
       <c r="R121" t="n">
-        <v>214.85</v>
+        <v>416.67</v>
       </c>
       <c r="S121" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="T121" t="n">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="U121" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="V121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W121" t="n">
         <v>0</v>
@@ -19196,34 +19184,34 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z121" t="n">
         <v>0</v>
       </c>
       <c r="AA121" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="AB121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>479</v>
+        <v>544</v>
       </c>
       <c r="AD121" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="AE121" t="n">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="AF121" t="n">
-        <v>242</v>
+        <v>266</v>
       </c>
       <c r="AG121" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AH121" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AI121" t="n">
         <v>0</v>
@@ -19232,81 +19220,81 @@
         <v>0</v>
       </c>
       <c r="AK121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AL121" t="n">
         <v>0</v>
       </c>
       <c r="AM121" t="n">
-        <v>43</v>
+        <v>96</v>
       </c>
       <c r="AN121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO121" t="n">
-        <v>479</v>
+        <v>544</v>
       </c>
       <c r="AP121" t="n">
-        <v>292</v>
+        <v>380</v>
       </c>
       <c r="AQ121" t="n">
-        <v>379</v>
+        <v>164</v>
       </c>
       <c r="AR121" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AS121" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AT121" t="n">
         <v>0</v>
       </c>
       <c r="AU121" t="n">
-        <v>0</v>
+        <v>266</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Muhamad Fadly Djafar</t>
+          <t>Ambrosius Tampi Tangkabiringan</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>tentangsangihe@gmail.com</t>
+          <t>tangkabiringanayen70@gmail.com</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Hastuti Manabung</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>hmanabung01@gmail.com</t>
+          <t>georgemulersasiangsasiang@gmail.com</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>(110) KENDAHE</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Herison</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G122" t="n">
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I122" t="n">
-        <v>63</v>
+        <v>178</v>
       </c>
       <c r="J122" t="n">
-        <v>64</v>
+        <v>178</v>
       </c>
       <c r="K122" t="n">
         <v>0</v>
@@ -19315,34 +19303,34 @@
         <v>0</v>
       </c>
       <c r="M122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N122" t="n">
-        <v>7.69</v>
+        <v>0</v>
       </c>
       <c r="O122" t="n">
-        <v>17</v>
+        <v>118</v>
       </c>
       <c r="P122" t="n">
-        <v>134.65</v>
+        <v>214.85</v>
       </c>
       <c r="Q122" t="n">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="R122" t="n">
-        <v>142.34</v>
+        <v>214.85</v>
       </c>
       <c r="S122" t="n">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="T122" t="n">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="U122" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="V122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W122" t="n">
         <v>0</v>
@@ -19351,34 +19339,34 @@
         <v>0</v>
       </c>
       <c r="Y122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z122" t="n">
         <v>0</v>
       </c>
       <c r="AA122" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC122" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="AD122" t="n">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="AE122" t="n">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c r="AF122" t="n">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="AG122" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AH122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AI122" t="n">
         <v>0</v>
@@ -19387,81 +19375,81 @@
         <v>0</v>
       </c>
       <c r="AK122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL122" t="n">
         <v>0</v>
       </c>
       <c r="AM122" t="n">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="AN122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO122" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="AP122" t="n">
-        <v>359</v>
+        <v>292</v>
       </c>
       <c r="AQ122" t="n">
-        <v>419</v>
+        <v>185</v>
       </c>
       <c r="AR122" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AS122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT122" t="n">
         <v>0</v>
       </c>
       <c r="AU122" t="n">
-        <v>0</v>
+        <v>242</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Septian Sulaiman</t>
+          <t>Muhamad Fadly Djafar</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>tianfirnanda16@gmail.com</t>
+          <t>tentangsangihe@gmail.com</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ivonne Lariunaung</t>
+          <t>Hastuti Manabung</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>vonnelariunaung77560@gmail.com</t>
+          <t>hmanabung01@gmail.com</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(110) KENDAHE</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Herison</t>
         </is>
       </c>
       <c r="G123" t="n">
         <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="J123" t="n">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="K123" t="n">
         <v>0</v>
@@ -19470,130 +19458,130 @@
         <v>0</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="O123" t="n">
+        <v>17</v>
+      </c>
+      <c r="P123" t="n">
+        <v>134.65</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>18</v>
+      </c>
+      <c r="R123" t="n">
+        <v>142.34</v>
+      </c>
+      <c r="S123" t="n">
+        <v>126</v>
+      </c>
+      <c r="T123" t="n">
+        <v>256</v>
+      </c>
+      <c r="U123" t="n">
         <v>16</v>
       </c>
-      <c r="P123" t="n">
-        <v>200.7</v>
-      </c>
-      <c r="Q123" t="n">
+      <c r="V123" t="n">
+        <v>0</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>86</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>485</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>359</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>126</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>256</v>
+      </c>
+      <c r="AG123" t="n">
         <v>16</v>
       </c>
-      <c r="R123" t="n">
-        <v>200.7</v>
-      </c>
-      <c r="S123" t="n">
-        <v>97</v>
-      </c>
-      <c r="T123" t="n">
-        <v>338</v>
-      </c>
-      <c r="U123" t="n">
-        <v>0</v>
-      </c>
-      <c r="V123" t="n">
-        <v>3</v>
-      </c>
-      <c r="W123" t="n">
-        <v>1</v>
-      </c>
-      <c r="X123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y123" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z123" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA123" t="n">
-        <v>58</v>
-      </c>
-      <c r="AB123" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC123" t="n">
-        <v>498</v>
-      </c>
-      <c r="AD123" t="n">
-        <v>398</v>
-      </c>
-      <c r="AE123" t="n">
-        <v>97</v>
-      </c>
-      <c r="AF123" t="n">
-        <v>338</v>
-      </c>
-      <c r="AG123" t="n">
-        <v>0</v>
-      </c>
       <c r="AH123" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ123" t="n">
         <v>0</v>
       </c>
       <c r="AK123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL123" t="n">
         <v>0</v>
       </c>
       <c r="AM123" t="n">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="AN123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO123" t="n">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="AP123" t="n">
-        <v>398</v>
+        <v>359</v>
       </c>
       <c r="AQ123" t="n">
-        <v>432</v>
+        <v>126</v>
       </c>
       <c r="AR123" t="n">
         <v>0</v>
       </c>
       <c r="AS123" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AT123" t="n">
         <v>0</v>
       </c>
       <c r="AU123" t="n">
-        <v>3</v>
+        <v>256</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Rachmawati Kampi</t>
+          <t>Septian Sulaiman</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>tikamustika1704@gmail.com</t>
+          <t>tianfirnanda16@gmail.com</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ivonne Lariunaung</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>vonnelariunaung77560@gmail.com</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -19613,10 +19601,10 @@
         <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="J124" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="K124" t="n">
         <v>0</v>
@@ -19631,31 +19619,31 @@
         <v>0</v>
       </c>
       <c r="O124" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P124" t="n">
-        <v>348.22</v>
+        <v>250.7</v>
       </c>
       <c r="Q124" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="R124" t="n">
-        <v>348.22</v>
+        <v>250.7</v>
       </c>
       <c r="S124" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="T124" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="U124" t="n">
         <v>0</v>
       </c>
       <c r="V124" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="W124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X124" t="n">
         <v>0</v>
@@ -19667,31 +19655,31 @@
         <v>0</v>
       </c>
       <c r="AA124" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AB124" t="n">
         <v>1</v>
       </c>
       <c r="AC124" t="n">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="AD124" t="n">
         <v>371</v>
       </c>
       <c r="AE124" t="n">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="AF124" t="n">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
       </c>
       <c r="AH124" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AI124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ124" t="n">
         <v>0</v>
@@ -19703,75 +19691,75 @@
         <v>0</v>
       </c>
       <c r="AM124" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="AN124" t="n">
         <v>1</v>
       </c>
       <c r="AO124" t="n">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="AP124" t="n">
         <v>371</v>
       </c>
       <c r="AQ124" t="n">
-        <v>437</v>
+        <v>128</v>
       </c>
       <c r="AR124" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AS124" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU124" t="n">
-        <v>0</v>
+        <v>332</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Kristia Mirnawati Tumpias</t>
+          <t>Rachmawati Kampi</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>tumpiask@gmail.com</t>
+          <t>tikamustika1704@gmail.com</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I125" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J125" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K125" t="n">
         <v>0</v>
@@ -19786,28 +19774,28 @@
         <v>0</v>
       </c>
       <c r="O125" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="P125" t="n">
-        <v>193.75</v>
+        <v>348.22</v>
       </c>
       <c r="Q125" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="R125" t="n">
-        <v>193.75</v>
+        <v>348.22</v>
       </c>
       <c r="S125" t="n">
-        <v>0</v>
+        <v>141</v>
       </c>
       <c r="T125" t="n">
-        <v>288</v>
+        <v>326</v>
       </c>
       <c r="U125" t="n">
         <v>0</v>
       </c>
       <c r="V125" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W125" t="n">
         <v>0</v>
@@ -19816,104 +19804,104 @@
         <v>0</v>
       </c>
       <c r="Y125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>514</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>371</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>141</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>326</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH125" t="n">
         <v>2</v>
       </c>
-      <c r="Z125" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA125" t="n">
-        <v>79</v>
-      </c>
-      <c r="AB125" t="n">
+      <c r="AI125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>44</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>514</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>371</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>141</v>
+      </c>
+      <c r="AR125" t="n">
         <v>2</v>
       </c>
-      <c r="AC125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AD125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AE125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF125" t="n">
-        <v>288</v>
-      </c>
-      <c r="AG125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ125" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK125" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL125" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM125" t="n">
-        <v>79</v>
-      </c>
-      <c r="AN125" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AP125" t="n">
-        <v>372</v>
-      </c>
-      <c r="AQ125" t="n">
-        <v>303</v>
-      </c>
-      <c r="AR125" t="n">
-        <v>0</v>
-      </c>
       <c r="AS125" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AT125" t="n">
         <v>0</v>
       </c>
       <c r="AU125" t="n">
-        <v>0</v>
+        <v>326</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Don Albert Seimahuira</t>
+          <t>Kristia Mirnawati Tumpias</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>ungkealbert39@gmail.com</t>
+          <t>tumpiask@gmail.com</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -19923,10 +19911,10 @@
         <v>0</v>
       </c>
       <c r="I126" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J126" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K126" t="n">
         <v>0</v>
@@ -19941,147 +19929,147 @@
         <v>0</v>
       </c>
       <c r="O126" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="P126" t="n">
-        <v>210.28</v>
+        <v>193.75</v>
       </c>
       <c r="Q126" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="R126" t="n">
-        <v>210.28</v>
+        <v>193.75</v>
       </c>
       <c r="S126" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="U126" t="n">
+        <v>0</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y126" t="n">
         <v>2</v>
       </c>
-      <c r="V126" t="n">
-        <v>0</v>
-      </c>
-      <c r="W126" t="n">
-        <v>0</v>
-      </c>
-      <c r="X126" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y126" t="n">
-        <v>1</v>
-      </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA126" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="AB126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC126" t="n">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="AD126" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="AE126" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="AF126" t="n">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="AG126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK126" t="n">
         <v>2</v>
       </c>
-      <c r="AH126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ126" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK126" t="n">
-        <v>1</v>
-      </c>
       <c r="AL126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM126" t="n">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="AN126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO126" t="n">
-        <v>441</v>
+        <v>372</v>
       </c>
       <c r="AP126" t="n">
-        <v>340</v>
+        <v>372</v>
       </c>
       <c r="AQ126" t="n">
-        <v>366</v>
+        <v>0</v>
       </c>
       <c r="AR126" t="n">
         <v>0</v>
       </c>
       <c r="AS126" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT126" t="n">
         <v>0</v>
       </c>
       <c r="AU126" t="n">
-        <v>0</v>
+        <v>288</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Verawati Cristy Lolaroh</t>
+          <t>Don Albert Seimahuira</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>verawaticristylolaroh02@gmail.com</t>
+          <t>ungkealbert39@gmail.com</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Jenie Oktavin Rahmawati Monok</t>
+          <t>Ferdinand Tangkabiringan</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>jeniemonok7@gmail.com</t>
+          <t>ferdinandtangkabiringan@gmail.com</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>(091) TAHUNA TIMUR</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Djon</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G127" t="n">
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" t="n">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="J127" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="K127" t="n">
         <v>0</v>
@@ -20096,134 +20084,134 @@
         <v>0</v>
       </c>
       <c r="O127" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="P127" t="n">
-        <v>1109.72</v>
+        <v>210.28</v>
       </c>
       <c r="Q127" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="R127" t="n">
-        <v>1109.72</v>
+        <v>210.28</v>
       </c>
       <c r="S127" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="T127" t="n">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="U127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V127" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="W127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="X127" t="n">
         <v>0</v>
       </c>
       <c r="Y127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z127" t="n">
         <v>0</v>
       </c>
       <c r="AA127" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="AB127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC127" t="n">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="AD127" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AE127" t="n">
-        <v>142</v>
+        <v>101</v>
       </c>
       <c r="AF127" t="n">
-        <v>268</v>
+        <v>306</v>
       </c>
       <c r="AG127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH127" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AI127" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AJ127" t="n">
         <v>0</v>
       </c>
       <c r="AK127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL127" t="n">
         <v>0</v>
       </c>
       <c r="AM127" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="AN127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO127" t="n">
-        <v>505</v>
+        <v>441</v>
       </c>
       <c r="AP127" t="n">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="AQ127" t="n">
-        <v>394</v>
+        <v>101</v>
       </c>
       <c r="AR127" t="n">
         <v>0</v>
       </c>
       <c r="AS127" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AT127" t="n">
         <v>0</v>
       </c>
       <c r="AU127" t="n">
-        <v>1</v>
+        <v>306</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Erin Fernanda Wenas</t>
+          <t>Verawati Cristy Lolaroh</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>wenaserin@gmail.com</t>
+          <t>verawaticristylolaroh02@gmail.com</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>George Muler Sasiang</t>
+          <t>Jenie Oktavin Rahmawati Monok</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>georgemulersasiangsasiang@gmail.com</t>
+          <t>jeniemonok7@gmail.com</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(091) TAHUNA TIMUR</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Djon</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -20233,10 +20221,10 @@
         <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="J128" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="K128" t="n">
         <v>0</v>
@@ -20251,67 +20239,67 @@
         <v>0</v>
       </c>
       <c r="O128" t="n">
+        <v>19</v>
+      </c>
+      <c r="P128" t="n">
+        <v>1109.72</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>19</v>
+      </c>
+      <c r="R128" t="n">
+        <v>1109.72</v>
+      </c>
+      <c r="S128" t="n">
+        <v>142</v>
+      </c>
+      <c r="T128" t="n">
+        <v>268</v>
+      </c>
+      <c r="U128" t="n">
+        <v>1</v>
+      </c>
+      <c r="V128" t="n">
         <v>27</v>
       </c>
-      <c r="P128" t="n">
-        <v>249.59</v>
-      </c>
-      <c r="Q128" t="n">
+      <c r="W128" t="n">
+        <v>4</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>63</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>505</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>336</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>142</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>268</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH128" t="n">
         <v>27</v>
       </c>
-      <c r="R128" t="n">
-        <v>249.59</v>
-      </c>
-      <c r="S128" t="n">
-        <v>131</v>
-      </c>
-      <c r="T128" t="n">
-        <v>317</v>
-      </c>
-      <c r="U128" t="n">
-        <v>5</v>
-      </c>
-      <c r="V128" t="n">
-        <v>13</v>
-      </c>
-      <c r="W128" t="n">
-        <v>2</v>
-      </c>
-      <c r="X128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA128" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC128" t="n">
-        <v>481</v>
-      </c>
-      <c r="AD128" t="n">
-        <v>337</v>
-      </c>
-      <c r="AE128" t="n">
-        <v>131</v>
-      </c>
-      <c r="AF128" t="n">
-        <v>317</v>
-      </c>
-      <c r="AG128" t="n">
-        <v>5</v>
-      </c>
-      <c r="AH128" t="n">
-        <v>13</v>
-      </c>
       <c r="AI128" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AJ128" t="n">
         <v>0</v>
@@ -20323,75 +20311,75 @@
         <v>0</v>
       </c>
       <c r="AM128" t="n">
-        <v>13</v>
+        <v>63</v>
       </c>
       <c r="AN128" t="n">
         <v>0</v>
       </c>
       <c r="AO128" t="n">
-        <v>481</v>
+        <v>505</v>
       </c>
       <c r="AP128" t="n">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AQ128" t="n">
-        <v>372</v>
+        <v>142</v>
       </c>
       <c r="AR128" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AS128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AT128" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU128" t="n">
-        <v>0</v>
+        <v>268</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Winda Metia</t>
+          <t>Erin Fernanda Wenas</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>windametia67@gmail.com</t>
+          <t>wenaserin@gmail.com</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Jeferson Manahampi</t>
+          <t>George Muler Sasiang</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>manahampijeferson94@gmail.com</t>
+          <t>georgemulersasiangsasiang@gmail.com</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>(040) MANGANITU SELATAN</t>
+          <t>(090) TAHUNA</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Fin</t>
+          <t>Yetty</t>
         </is>
       </c>
       <c r="G129" t="n">
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I129" t="n">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="J129" t="n">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="K129" t="n">
         <v>0</v>
@@ -20406,31 +20394,31 @@
         <v>0</v>
       </c>
       <c r="O129" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="P129" t="n">
-        <v>87.88</v>
+        <v>249.59</v>
       </c>
       <c r="Q129" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="R129" t="n">
-        <v>87.88</v>
+        <v>249.59</v>
       </c>
       <c r="S129" t="n">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="T129" t="n">
-        <v>187</v>
+        <v>317</v>
       </c>
       <c r="U129" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="V129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W129" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X129" t="n">
         <v>0</v>
@@ -20442,88 +20430,88 @@
         <v>0</v>
       </c>
       <c r="AA129" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="AB129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC129" t="n">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="AD129" t="n">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="AE129" t="n">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="AF129" t="n">
-        <v>189</v>
+        <v>317</v>
       </c>
       <c r="AG129" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AH129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AI129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ129" t="n">
         <v>0</v>
       </c>
       <c r="AK129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL129" t="n">
         <v>0</v>
       </c>
       <c r="AM129" t="n">
-        <v>99</v>
+        <v>13</v>
       </c>
       <c r="AN129" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO129" t="n">
-        <v>360</v>
+        <v>481</v>
       </c>
       <c r="AP129" t="n">
-        <v>301</v>
+        <v>337</v>
       </c>
       <c r="AQ129" t="n">
-        <v>313</v>
+        <v>131</v>
       </c>
       <c r="AR129" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AS129" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT129" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AU129" t="n">
-        <v>1</v>
+        <v>317</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Yosua Bawembang</t>
+          <t>Winda Metia</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ybawembang@gmail.com</t>
+          <t>windametia67@gmail.com</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Johny Steven Manoppo</t>
+          <t>Jeferson Manahampi</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>stevenmanoppo36@gmail.com</t>
+          <t>manahampijeferson94@gmail.com</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -20540,13 +20528,13 @@
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I130" t="n">
-        <v>107</v>
+        <v>15</v>
       </c>
       <c r="J130" t="n">
-        <v>108</v>
+        <v>15</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -20561,31 +20549,31 @@
         <v>0</v>
       </c>
       <c r="O130" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="P130" t="n">
-        <v>139.02</v>
+        <v>87.88</v>
       </c>
       <c r="Q130" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="R130" t="n">
-        <v>139.02</v>
+        <v>87.88</v>
       </c>
       <c r="S130" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="T130" t="n">
-        <v>307</v>
+        <v>187</v>
       </c>
       <c r="U130" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="V130" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X130" t="n">
         <v>0</v>
@@ -20597,28 +20585,28 @@
         <v>0</v>
       </c>
       <c r="AA130" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="AB130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AC130" t="n">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="AD130" t="n">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="AE130" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AF130" t="n">
-        <v>307</v>
+        <v>189</v>
       </c>
       <c r="AG130" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AH130" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="AI130" t="n">
         <v>0</v>
@@ -20627,81 +20615,81 @@
         <v>0</v>
       </c>
       <c r="AK130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL130" t="n">
         <v>0</v>
       </c>
       <c r="AM130" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="AN130" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO130" t="n">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="AP130" t="n">
-        <v>334</v>
+        <v>301</v>
       </c>
       <c r="AQ130" t="n">
-        <v>386</v>
+        <v>59</v>
       </c>
       <c r="AR130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS130" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="AT130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU130" t="n">
-        <v>1</v>
+        <v>187</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Yudhistira Prasetya Tangkabiringan</t>
+          <t>Yosua Bawembang</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>yudhistiratangkabiringan@gmail.com</t>
+          <t>ybawembang@gmail.com</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ferdinand Tangkabiringan</t>
+          <t>Johny Steven Manoppo</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ferdinandtangkabiringan@gmail.com</t>
+          <t>stevenmanoppo36@gmail.com</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>(090) TAHUNA</t>
+          <t>(040) MANGANITU SELATAN</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Yetty</t>
+          <t>Fin</t>
         </is>
       </c>
       <c r="G131" t="n">
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="J131" t="n">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -20716,28 +20704,28 @@
         <v>0</v>
       </c>
       <c r="O131" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="P131" t="n">
-        <v>140</v>
+        <v>139.02</v>
       </c>
       <c r="Q131" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="R131" t="n">
-        <v>140</v>
+        <v>139.02</v>
       </c>
       <c r="S131" t="n">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="T131" t="n">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="U131" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V131" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="W131" t="n">
         <v>0</v>
@@ -20752,28 +20740,28 @@
         <v>0</v>
       </c>
       <c r="AA131" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AB131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC131" t="n">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="AD131" t="n">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="AE131" t="n">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="AF131" t="n">
-        <v>209</v>
+        <v>307</v>
       </c>
       <c r="AG131" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AH131" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="AI131" t="n">
         <v>0</v>
@@ -20788,186 +20776,341 @@
         <v>0</v>
       </c>
       <c r="AM131" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="AN131" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO131" t="n">
-        <v>400</v>
+        <v>447</v>
       </c>
       <c r="AP131" t="n">
-        <v>261</v>
+        <v>334</v>
       </c>
       <c r="AQ131" t="n">
-        <v>370</v>
+        <v>61</v>
       </c>
       <c r="AR131" t="n">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="AS131" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT131" t="n">
         <v>0</v>
       </c>
       <c r="AU131" t="n">
-        <v>0</v>
+        <v>307</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>Yudhistira Prasetya Tangkabiringan</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>yudhistiratangkabiringan@gmail.com</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ferdinand Tangkabiringan</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ferdinandtangkabiringan@gmail.com</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>(090) TAHUNA</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Yetty</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>22</v>
+      </c>
+      <c r="J132" t="n">
+        <v>22</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>9</v>
+      </c>
+      <c r="P132" t="n">
+        <v>140</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>9</v>
+      </c>
+      <c r="R132" t="n">
+        <v>140</v>
+      </c>
+      <c r="S132" t="n">
+        <v>139</v>
+      </c>
+      <c r="T132" t="n">
+        <v>209</v>
+      </c>
+      <c r="U132" t="n">
+        <v>6</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>46</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>400</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>261</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>139</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>209</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>46</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>400</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>261</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>139</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
           <t>Yustin Durian</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B133" t="inlineStr">
         <is>
           <t>yustindurian@gmail.com</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Fiane Greti Mansauda</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D133" t="inlineStr">
         <is>
           <t>fianemansauda89@gmail.com</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
+      <c r="E133" t="inlineStr">
         <is>
           <t>(070) TABUKAN TENGAH</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F133" t="inlineStr">
         <is>
           <t>Kharis</t>
         </is>
       </c>
-      <c r="G132" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" t="n">
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
         <v>24</v>
       </c>
-      <c r="J132" t="n">
+      <c r="J133" t="n">
         <v>24</v>
       </c>
-      <c r="K132" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" t="n">
-        <v>0</v>
-      </c>
-      <c r="N132" t="n">
-        <v>0</v>
-      </c>
-      <c r="O132" t="n">
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" t="n">
         <v>17</v>
       </c>
-      <c r="P132" t="n">
+      <c r="P133" t="n">
         <v>400</v>
       </c>
-      <c r="Q132" t="n">
+      <c r="Q133" t="n">
         <v>17</v>
       </c>
-      <c r="R132" t="n">
+      <c r="R133" t="n">
         <v>400</v>
       </c>
-      <c r="S132" t="n">
+      <c r="S133" t="n">
         <v>131</v>
       </c>
-      <c r="T132" t="n">
+      <c r="T133" t="n">
         <v>278</v>
       </c>
-      <c r="U132" t="n">
+      <c r="U133" t="n">
         <v>2</v>
       </c>
-      <c r="V132" t="n">
-        <v>0</v>
-      </c>
-      <c r="W132" t="n">
-        <v>0</v>
-      </c>
-      <c r="X132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y132" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA132" t="n">
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" t="n">
         <v>43</v>
       </c>
-      <c r="AB132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC132" t="n">
+      <c r="AB133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC133" t="n">
         <v>456</v>
       </c>
-      <c r="AD132" t="n">
+      <c r="AD133" t="n">
         <v>325</v>
       </c>
-      <c r="AE132" t="n">
+      <c r="AE133" t="n">
         <v>131</v>
       </c>
-      <c r="AF132" t="n">
+      <c r="AF133" t="n">
         <v>278</v>
       </c>
-      <c r="AG132" t="n">
+      <c r="AG133" t="n">
         <v>2</v>
       </c>
-      <c r="AH132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM132" t="n">
+      <c r="AH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM133" t="n">
         <v>43</v>
       </c>
-      <c r="AN132" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO132" t="n">
+      <c r="AN133" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO133" t="n">
         <v>456</v>
       </c>
-      <c r="AP132" t="n">
+      <c r="AP133" t="n">
         <v>325</v>
       </c>
-      <c r="AQ132" t="n">
-        <v>368</v>
-      </c>
-      <c r="AR132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS132" t="n">
-        <v>3</v>
-      </c>
-      <c r="AT132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU132" t="n">
-        <v>0</v>
+      <c r="AQ133" t="n">
+        <v>131</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>278</v>
       </c>
     </row>
   </sheetData>
